--- a/template_taisan.xlsx
+++ b/template_taisan.xlsx
@@ -1,441 +1,469 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B413445-E037-4550-91A6-4C2293E85C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="5"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="profiles" sheetId="13" r:id="rId1"/>
-    <sheet name="departments" sheetId="14" r:id="rId2"/>
-    <sheet name="Locations" sheetId="3" r:id="rId3"/>
-    <sheet name="Categories" sheetId="5" r:id="rId4"/>
-    <sheet name="Vendors" sheetId="7" r:id="rId5"/>
-    <sheet name="Parts" sheetId="9" r:id="rId6"/>
-    <sheet name="Assets" sheetId="11" r:id="rId7"/>
-    <sheet name="importLocations" sheetId="4" r:id="rId8"/>
-    <sheet name="importCategories" sheetId="6" r:id="rId9"/>
-    <sheet name="importVendors" sheetId="8" r:id="rId10"/>
-    <sheet name="importParts" sheetId="10" r:id="rId11"/>
-    <sheet name="importAssets" sheetId="12" r:id="rId12"/>
+    <sheet name="profiles" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="departments" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Locations" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Categories" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Vendors" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Parts" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Assets" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="importLocations" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="importCategories" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="importVendors" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="importParts" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="importAssets" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="121">
   <si>
-    <t>Mã nhân viên</t>
-  </si>
-  <si>
-    <t>Họ và Tên</t>
-  </si>
-  <si>
-    <t>Số điện thoại</t>
-  </si>
-  <si>
-    <t>Email Công ty</t>
-  </si>
-  <si>
-    <t>Email cá nhân</t>
-  </si>
-  <si>
-    <t>Chức danh</t>
-  </si>
-  <si>
-    <t>Vai trò</t>
-  </si>
-  <si>
-    <t>Mã phòng ban</t>
-  </si>
-  <si>
-    <t>Tên phòng ban</t>
-  </si>
-  <si>
-    <t>Mã người quản lý</t>
-  </si>
-  <si>
-    <t>Tên người quản lý</t>
-  </si>
-  <si>
-    <t>Tình trạng</t>
-  </si>
-  <si>
-    <t>Phân quyền</t>
-  </si>
-  <si>
-    <t>Phòng Kinh doanh</t>
-  </si>
-  <si>
-    <t>Phòng Dự án</t>
-  </si>
-  <si>
-    <t>Xưởng Dịch vụ</t>
-  </si>
-  <si>
-    <t>Phòng Kỹ thuật</t>
-  </si>
-  <si>
-    <t>Phòng Mua hàng</t>
-  </si>
-  <si>
-    <t>Phòng Kế hoạch</t>
-  </si>
-  <si>
-    <t>EMM</t>
-  </si>
-  <si>
-    <t>Mã trưởng phòng</t>
-  </si>
-  <si>
-    <t>Tên trưởng phòng</t>
-  </si>
-  <si>
-    <t>XD</t>
-  </si>
-  <si>
-    <t>Xưởng Điện</t>
-  </si>
-  <si>
-    <t>Mã vị trí*</t>
-  </si>
-  <si>
-    <t>Tên vị trí*</t>
-  </si>
-  <si>
-    <t>Mã vị trí cha</t>
-  </si>
-  <si>
-    <t>Loại vị trí</t>
-  </si>
-  <si>
-    <t>Mô tả</t>
-  </si>
-  <si>
-    <t>Kích hoạt</t>
-  </si>
-  <si>
-    <t>Mã loại TS*</t>
-  </si>
-  <si>
-    <t>Tên loại TS*</t>
-  </si>
-  <si>
-    <t>Mã phòng ban quản lý*</t>
-  </si>
-  <si>
-    <t>Mã loại TS cha</t>
-  </si>
-  <si>
-    <t>Mã nhà cung cấp*</t>
-  </si>
-  <si>
-    <t>Tên công ty</t>
-  </si>
-  <si>
-    <t>Mã số thuế</t>
-  </si>
-  <si>
-    <t>Số TK</t>
-  </si>
-  <si>
-    <t>Ngân hàng</t>
-  </si>
-  <si>
-    <t>Người liên hệ</t>
-  </si>
-  <si>
-    <t>SĐT</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Địa chỉ</t>
-  </si>
-  <si>
-    <t>Dịch vụ cung cấp</t>
-  </si>
-  <si>
-    <t>Ghi chú</t>
-  </si>
-  <si>
-    <t>Mã phụ tùng*</t>
-  </si>
-  <si>
-    <t>Tên phụ tùng*</t>
-  </si>
-  <si>
-    <t>Nhóm</t>
-  </si>
-  <si>
-    <t>Đơn vị tính</t>
-  </si>
-  <si>
-    <t>Tồn kho hiện tại</t>
-  </si>
-  <si>
-    <t>Tồn kho tối thiểu</t>
-  </si>
-  <si>
-    <t>Đơn giá</t>
-  </si>
-  <si>
-    <t>Mã tài sản*</t>
-  </si>
-  <si>
-    <t>Tên tài sản*</t>
-  </si>
-  <si>
-    <t>Trạng thái</t>
-  </si>
-  <si>
-    <t>Mã nhà cung cấp</t>
-  </si>
-  <si>
-    <t>Mã vị trí hiện tại</t>
-  </si>
-  <si>
-    <t>Mã NV đang giữ</t>
-  </si>
-  <si>
-    <t>Nhãn hiệu</t>
-  </si>
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Serial Number</t>
-  </si>
-  <si>
-    <t>Thông số/Cấu hình</t>
-  </si>
-  <si>
-    <t>Ngày mua</t>
-  </si>
-  <si>
-    <t>Giá trước thuế</t>
-  </si>
-  <si>
-    <t>Giá sau thuế</t>
-  </si>
-  <si>
-    <t>Hạn bảo hành</t>
-  </si>
-  <si>
-    <t>VP</t>
-  </si>
-  <si>
-    <t>Văn phòng</t>
-  </si>
-  <si>
-    <t>Nhà văn phòng tại Đông Anh</t>
-  </si>
-  <si>
-    <t>Công ty</t>
-  </si>
-  <si>
-    <t>DNB</t>
-  </si>
-  <si>
-    <t>Đường nội bộ</t>
-  </si>
-  <si>
-    <t>Đường đi</t>
-  </si>
-  <si>
-    <t>Các đường nội bộ giữa văn phòng, kho, xưởng</t>
-  </si>
-  <si>
-    <t>HLT1</t>
-  </si>
-  <si>
-    <t>HLT2</t>
-  </si>
-  <si>
-    <t>Hành lang tầng 1</t>
-  </si>
-  <si>
-    <t>Hành lang tầng 2</t>
-  </si>
-  <si>
-    <t>KTP</t>
-  </si>
-  <si>
-    <t>Kho thành phẩm</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>Sảnh lễ tân</t>
-  </si>
-  <si>
-    <t>canteen</t>
-  </si>
-  <si>
-    <t>Nhà ăn</t>
-  </si>
-  <si>
-    <t>P.DA</t>
-  </si>
-  <si>
-    <t>P.GDSX</t>
-  </si>
-  <si>
-    <t>Phòng Giám đốc Sản xuất</t>
-  </si>
-  <si>
-    <t>P.HCNS</t>
-  </si>
-  <si>
-    <t>Phòng Hành chính Nhân sự</t>
-  </si>
-  <si>
-    <t>Phòng họp số 1</t>
-  </si>
-  <si>
-    <t>Phòng họp số 2</t>
-  </si>
-  <si>
-    <t>Phòng Kế toán trưởng</t>
-  </si>
-  <si>
-    <t>Phòng Kiểm soát nội bộ</t>
-  </si>
-  <si>
-    <t>Phòng Máy tính</t>
-  </si>
-  <si>
-    <t>Phòng Phó Tổng giám đốc</t>
-  </si>
-  <si>
-    <t>Phòng QC</t>
-  </si>
-  <si>
-    <t>Phòng QC Xưởng Dịch vụ</t>
-  </si>
-  <si>
-    <t>Phòng Tài chính Kế toán</t>
-  </si>
-  <si>
-    <t>Phòng Tổng Giám Đốc</t>
-  </si>
-  <si>
-    <t>Showroom</t>
-  </si>
-  <si>
-    <t>Văn phòng Xưởng Dịch vụ</t>
-  </si>
-  <si>
-    <t>Văn phòng Xưởng Điện</t>
-  </si>
-  <si>
-    <t>PH1</t>
-  </si>
-  <si>
-    <t>PH2</t>
-  </si>
-  <si>
-    <t>KCS.XD</t>
-  </si>
-  <si>
-    <t>P.KH</t>
-  </si>
-  <si>
-    <t>P.KTT</t>
-  </si>
-  <si>
-    <t>P.KSNB</t>
-  </si>
-  <si>
-    <t>P.KD</t>
-  </si>
-  <si>
-    <t>P.KT</t>
-  </si>
-  <si>
-    <t>P.MT</t>
-  </si>
-  <si>
-    <t>P.MH</t>
-  </si>
-  <si>
-    <t>P.PTGD</t>
-  </si>
-  <si>
-    <t>P.QC</t>
-  </si>
-  <si>
-    <t>QC.XDV</t>
-  </si>
-  <si>
-    <t>P.TCKT</t>
-  </si>
-  <si>
-    <t>P.TGD</t>
-  </si>
-  <si>
-    <t>VP.XDV</t>
-  </si>
-  <si>
-    <t>VP.XD</t>
-  </si>
-  <si>
-    <t>XDV</t>
-  </si>
-  <si>
-    <t>Phòng KCS Xưởng Điện</t>
+    <t xml:space="preserve">Mã nhân viên</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Họ và Tên</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số điện thoại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email Công ty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email cá nhân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chức danh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vai trò</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mã phòng ban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tên phòng ban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mã người quản lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tên người quản lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tình trạng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phân quyền</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mã trưởng phòng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tên trưởng phòng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mã vị trí*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tên vị trí*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mã vị trí cha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loại vị trí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mô tả</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kích hoạt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Công ty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Văn phòng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhà văn phòng tại Đông Anh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đường nội bộ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đường đi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Các đường nội bộ giữa văn phòng, kho, xưởng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xưởng Dịch vụ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xưởng Điện</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HLT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hành lang tầng 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HLT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hành lang tầng 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KTP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kho thành phẩm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sảnh lễ tân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canteen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhà ăn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.DA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phòng Dự án</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.GDSX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phòng Giám đốc Sản xuất</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.HCNS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phòng Hành chính Nhân sự</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phòng họp số 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phòng họp số 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KCS.XD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phòng KCS Xưởng Điện</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phòng Kế hoạch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.KTT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phòng Kế toán trưởng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.KSNB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phòng Kiểm soát nội bộ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.KD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phòng Kinh doanh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.KT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phòng Kỹ thuật</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.MT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phòng Máy tính</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.MH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phòng Mua hàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.PTGD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phòng Phó Tổng giám đốc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.QC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phòng QC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QC.XDV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phòng QC Xưởng Dịch vụ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.TCKT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phòng Tài chính Kế toán</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.TGD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phòng Tổng Giám Đốc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Showroom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VP.XDV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Văn phòng Xưởng Dịch vụ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VP.XD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Văn phòng Xưởng Điện</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mã loại TS*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tên loại TS*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mã phòng ban quản lý*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mã loại TS cha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mã nhà cung cấp*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tên công ty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mã số thuế</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số TK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ngân hàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Người liên hệ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SĐT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Địa chỉ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dịch vụ cung cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghi chú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mã phụ tùng*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tên phụ tùng*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhóm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đơn vị tính</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tồn kho hiện tại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tồn kho tối thiểu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đơn giá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mã tài sản*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tên tài sản*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trạng thái</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mã nhà cung cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mã vị trí hiện tại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mã NV đang giữ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhãn hiệu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serial Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thông số/Cấu hình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ngày mua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giá trước thuế</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giá sau thuế</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hạn bảo hành</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="10"/>
       <color theme="0"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -445,25 +473,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFED8936"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED8936"/>
         <bgColor rgb="FFFF8080"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
-    <border>
+  <borders count="2">
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color theme="1"/>
       </left>
@@ -478,69 +500,158 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+  <cellXfs count="11">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
-    <mruColors>
-      <color rgb="FFED8936"/>
-    </mruColors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFED8936"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -575,304 +686,158 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="100000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:M500"/>
-  <sheetFormatPr defaultColWidth="13.28515625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.2890625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" style="1" customWidth="1"/>
-    <col min="4" max="6" width="38.5703125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16" style="1" customWidth="1"/>
-    <col min="9" max="9" width="38.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="28.85546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.85546875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="116.42578125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="13.28515625" style="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="38.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="38.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="19.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="28.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="15.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="116.42"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="14" style="2" width="13.29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -913,7 +878,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -928,7 +893,7 @@
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
-    <row r="3" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -943,7 +908,7 @@
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
     </row>
-    <row r="4" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -958,7 +923,7 @@
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
-    <row r="5" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -973,7 +938,7 @@
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
-    <row r="6" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -988,7 +953,7 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -1003,7 +968,7 @@
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
-    <row r="8" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1018,7 +983,7 @@
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
-    <row r="9" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -1033,7 +998,7 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -1048,7 +1013,7 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
-    <row r="11" spans="1:13" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" s="1" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1063,7 +1028,7 @@
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
     </row>
-    <row r="12" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -1078,7 +1043,7 @@
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
     </row>
-    <row r="13" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -1093,7 +1058,7 @@
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
     </row>
-    <row r="14" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -1108,7 +1073,7 @@
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
     </row>
-    <row r="15" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -1123,7 +1088,7 @@
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -1138,7 +1103,7 @@
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
     </row>
-    <row r="17" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -1153,7 +1118,7 @@
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
     </row>
-    <row r="18" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -1168,7 +1133,7 @@
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
     </row>
-    <row r="19" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -1183,7 +1148,7 @@
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
     </row>
-    <row r="20" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -1198,7 +1163,7 @@
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
     </row>
-    <row r="21" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1213,7 +1178,7 @@
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
     </row>
-    <row r="22" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1228,7 +1193,7 @@
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
     </row>
-    <row r="23" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1243,7 +1208,7 @@
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
     </row>
-    <row r="24" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -1258,7 +1223,7 @@
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
     </row>
-    <row r="25" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1273,7 +1238,7 @@
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
     </row>
-    <row r="26" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1288,7 +1253,7 @@
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
     </row>
-    <row r="27" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1303,7 +1268,7 @@
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
     </row>
-    <row r="28" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1318,7 +1283,7 @@
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
     </row>
-    <row r="29" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -1333,7 +1298,7 @@
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
     </row>
-    <row r="30" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -1348,7 +1313,7 @@
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
     </row>
-    <row r="31" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -1363,7 +1328,7 @@
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
     </row>
-    <row r="32" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -1378,7 +1343,7 @@
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
     </row>
-    <row r="33" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -1393,7 +1358,7 @@
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
     </row>
-    <row r="34" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -1408,7 +1373,7 @@
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
     </row>
-    <row r="35" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -1423,7 +1388,7 @@
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
     </row>
-    <row r="36" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -1438,7 +1403,7 @@
       <c r="L36" s="4"/>
       <c r="M36" s="4"/>
     </row>
-    <row r="37" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -1453,7 +1418,7 @@
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
     </row>
-    <row r="38" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -1468,7 +1433,7 @@
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
     </row>
-    <row r="39" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -1483,7 +1448,7 @@
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
     </row>
-    <row r="40" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -1498,7 +1463,7 @@
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
     </row>
-    <row r="41" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -1513,7 +1478,7 @@
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
     </row>
-    <row r="42" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -1528,7 +1493,7 @@
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
     </row>
-    <row r="43" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -1543,7 +1508,7 @@
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
     </row>
-    <row r="44" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -1558,7 +1523,7 @@
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
     </row>
-    <row r="45" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -1573,7 +1538,7 @@
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
     </row>
-    <row r="46" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -1588,7 +1553,7 @@
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
     </row>
-    <row r="47" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -1603,7 +1568,7 @@
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
     </row>
-    <row r="48" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -1618,7 +1583,7 @@
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
     </row>
-    <row r="49" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -1633,7 +1598,7 @@
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
     </row>
-    <row r="50" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -1648,7 +1613,7 @@
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
     </row>
-    <row r="51" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -1663,7 +1628,7 @@
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
     </row>
-    <row r="52" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -1678,7 +1643,7 @@
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
     </row>
-    <row r="53" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -1693,7 +1658,7 @@
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
     </row>
-    <row r="54" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -1708,7 +1673,7 @@
       <c r="L54" s="4"/>
       <c r="M54" s="4"/>
     </row>
-    <row r="55" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -1723,7 +1688,7 @@
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
     </row>
-    <row r="56" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -1738,7 +1703,7 @@
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
     </row>
-    <row r="57" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -1753,7 +1718,7 @@
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
     </row>
-    <row r="58" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -1768,7 +1733,7 @@
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
     </row>
-    <row r="59" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -1783,7 +1748,7 @@
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
     </row>
-    <row r="60" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -1798,7 +1763,7 @@
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
     </row>
-    <row r="61" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -1813,7 +1778,7 @@
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
     </row>
-    <row r="62" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -1828,7 +1793,7 @@
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
     </row>
-    <row r="63" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -1843,7 +1808,7 @@
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
     </row>
-    <row r="64" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -1858,7 +1823,7 @@
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
     </row>
-    <row r="65" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -1873,7 +1838,7 @@
       <c r="L65" s="4"/>
       <c r="M65" s="4"/>
     </row>
-    <row r="66" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -1888,7 +1853,7 @@
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
     </row>
-    <row r="67" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -1903,7 +1868,7 @@
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
     </row>
-    <row r="68" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -1918,7 +1883,7 @@
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
     </row>
-    <row r="69" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -1933,7 +1898,7 @@
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
     </row>
-    <row r="70" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -1948,7 +1913,7 @@
       <c r="L70" s="4"/>
       <c r="M70" s="4"/>
     </row>
-    <row r="71" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -1963,7 +1928,7 @@
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
     </row>
-    <row r="72" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -1978,7 +1943,7 @@
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
     </row>
-    <row r="73" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -1993,7 +1958,7 @@
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
     </row>
-    <row r="74" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -2008,7 +1973,7 @@
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
     </row>
-    <row r="75" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -2023,7 +1988,7 @@
       <c r="L75" s="4"/>
       <c r="M75" s="4"/>
     </row>
-    <row r="76" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -2038,7 +2003,7 @@
       <c r="L76" s="4"/>
       <c r="M76" s="4"/>
     </row>
-    <row r="77" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -2053,7 +2018,7 @@
       <c r="L77" s="4"/>
       <c r="M77" s="4"/>
     </row>
-    <row r="78" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -2068,7 +2033,7 @@
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
     </row>
-    <row r="79" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -2083,7 +2048,7 @@
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
     </row>
-    <row r="80" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -2098,7 +2063,7 @@
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
     </row>
-    <row r="81" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -2113,7 +2078,7 @@
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
     </row>
-    <row r="82" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -2128,7 +2093,7 @@
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
     </row>
-    <row r="83" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -2143,7 +2108,7 @@
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
     </row>
-    <row r="84" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -2158,7 +2123,7 @@
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
     </row>
-    <row r="85" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -2173,7 +2138,7 @@
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
     </row>
-    <row r="86" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -2188,7 +2153,7 @@
       <c r="L86" s="4"/>
       <c r="M86" s="4"/>
     </row>
-    <row r="87" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -2203,7 +2168,7 @@
       <c r="L87" s="4"/>
       <c r="M87" s="4"/>
     </row>
-    <row r="88" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -2218,7 +2183,7 @@
       <c r="L88" s="4"/>
       <c r="M88" s="4"/>
     </row>
-    <row r="89" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -2233,7 +2198,7 @@
       <c r="L89" s="4"/>
       <c r="M89" s="4"/>
     </row>
-    <row r="90" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -2248,7 +2213,7 @@
       <c r="L90" s="4"/>
       <c r="M90" s="4"/>
     </row>
-    <row r="91" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -2263,7 +2228,7 @@
       <c r="L91" s="4"/>
       <c r="M91" s="4"/>
     </row>
-    <row r="92" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -2278,7 +2243,7 @@
       <c r="L92" s="4"/>
       <c r="M92" s="4"/>
     </row>
-    <row r="93" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -2293,7 +2258,7 @@
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
     </row>
-    <row r="94" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -2308,7 +2273,7 @@
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
     </row>
-    <row r="95" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -2323,7 +2288,7 @@
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
     </row>
-    <row r="96" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -2338,7 +2303,7 @@
       <c r="L96" s="4"/>
       <c r="M96" s="4"/>
     </row>
-    <row r="97" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -2353,7 +2318,7 @@
       <c r="L97" s="4"/>
       <c r="M97" s="4"/>
     </row>
-    <row r="98" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -2368,7 +2333,7 @@
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
     </row>
-    <row r="99" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -2383,7 +2348,7 @@
       <c r="L99" s="4"/>
       <c r="M99" s="4"/>
     </row>
-    <row r="100" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -2398,7 +2363,7 @@
       <c r="L100" s="4"/>
       <c r="M100" s="4"/>
     </row>
-    <row r="101" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -2413,7 +2378,7 @@
       <c r="L101" s="4"/>
       <c r="M101" s="4"/>
     </row>
-    <row r="102" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -2428,7 +2393,7 @@
       <c r="L102" s="4"/>
       <c r="M102" s="4"/>
     </row>
-    <row r="103" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -2443,7 +2408,7 @@
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
     </row>
-    <row r="104" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -2458,7 +2423,7 @@
       <c r="L104" s="4"/>
       <c r="M104" s="4"/>
     </row>
-    <row r="105" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -2473,7 +2438,7 @@
       <c r="L105" s="4"/>
       <c r="M105" s="4"/>
     </row>
-    <row r="106" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -2488,7 +2453,7 @@
       <c r="L106" s="4"/>
       <c r="M106" s="4"/>
     </row>
-    <row r="107" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -2503,7 +2468,7 @@
       <c r="L107" s="4"/>
       <c r="M107" s="4"/>
     </row>
-    <row r="108" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -2518,7 +2483,7 @@
       <c r="L108" s="4"/>
       <c r="M108" s="4"/>
     </row>
-    <row r="109" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -2533,7 +2498,7 @@
       <c r="L109" s="4"/>
       <c r="M109" s="4"/>
     </row>
-    <row r="110" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -2548,7 +2513,7 @@
       <c r="L110" s="4"/>
       <c r="M110" s="4"/>
     </row>
-    <row r="111" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -2563,7 +2528,7 @@
       <c r="L111" s="4"/>
       <c r="M111" s="4"/>
     </row>
-    <row r="112" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -2578,7 +2543,7 @@
       <c r="L112" s="4"/>
       <c r="M112" s="4"/>
     </row>
-    <row r="113" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -2593,7 +2558,7 @@
       <c r="L113" s="4"/>
       <c r="M113" s="4"/>
     </row>
-    <row r="114" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -2608,7 +2573,7 @@
       <c r="L114" s="4"/>
       <c r="M114" s="4"/>
     </row>
-    <row r="115" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -2623,7 +2588,7 @@
       <c r="L115" s="4"/>
       <c r="M115" s="4"/>
     </row>
-    <row r="116" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -2638,7 +2603,7 @@
       <c r="L116" s="4"/>
       <c r="M116" s="4"/>
     </row>
-    <row r="117" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -2653,7 +2618,7 @@
       <c r="L117" s="4"/>
       <c r="M117" s="4"/>
     </row>
-    <row r="118" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -2668,7 +2633,7 @@
       <c r="L118" s="4"/>
       <c r="M118" s="4"/>
     </row>
-    <row r="119" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -2683,7 +2648,7 @@
       <c r="L119" s="4"/>
       <c r="M119" s="4"/>
     </row>
-    <row r="120" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -2698,7 +2663,7 @@
       <c r="L120" s="4"/>
       <c r="M120" s="4"/>
     </row>
-    <row r="121" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -2713,7 +2678,7 @@
       <c r="L121" s="4"/>
       <c r="M121" s="4"/>
     </row>
-    <row r="122" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -2728,7 +2693,7 @@
       <c r="L122" s="4"/>
       <c r="M122" s="4"/>
     </row>
-    <row r="123" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -2743,7 +2708,7 @@
       <c r="L123" s="4"/>
       <c r="M123" s="4"/>
     </row>
-    <row r="124" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -2758,7 +2723,7 @@
       <c r="L124" s="4"/>
       <c r="M124" s="4"/>
     </row>
-    <row r="125" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -2773,7 +2738,7 @@
       <c r="L125" s="4"/>
       <c r="M125" s="4"/>
     </row>
-    <row r="126" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -2788,7 +2753,7 @@
       <c r="L126" s="4"/>
       <c r="M126" s="4"/>
     </row>
-    <row r="127" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -2803,7 +2768,7 @@
       <c r="L127" s="4"/>
       <c r="M127" s="4"/>
     </row>
-    <row r="128" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -2818,7 +2783,7 @@
       <c r="L128" s="4"/>
       <c r="M128" s="4"/>
     </row>
-    <row r="129" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -2833,7 +2798,7 @@
       <c r="L129" s="4"/>
       <c r="M129" s="4"/>
     </row>
-    <row r="130" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -2848,7 +2813,7 @@
       <c r="L130" s="4"/>
       <c r="M130" s="4"/>
     </row>
-    <row r="131" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -2863,7 +2828,7 @@
       <c r="L131" s="4"/>
       <c r="M131" s="4"/>
     </row>
-    <row r="132" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
@@ -2878,7 +2843,7 @@
       <c r="L132" s="4"/>
       <c r="M132" s="4"/>
     </row>
-    <row r="133" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -2893,7 +2858,7 @@
       <c r="L133" s="4"/>
       <c r="M133" s="4"/>
     </row>
-    <row r="134" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -2908,7 +2873,7 @@
       <c r="L134" s="4"/>
       <c r="M134" s="4"/>
     </row>
-    <row r="135" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -2923,7 +2888,7 @@
       <c r="L135" s="4"/>
       <c r="M135" s="4"/>
     </row>
-    <row r="136" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -2938,7 +2903,7 @@
       <c r="L136" s="4"/>
       <c r="M136" s="4"/>
     </row>
-    <row r="137" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -2953,7 +2918,7 @@
       <c r="L137" s="4"/>
       <c r="M137" s="4"/>
     </row>
-    <row r="138" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -2968,7 +2933,7 @@
       <c r="L138" s="4"/>
       <c r="M138" s="4"/>
     </row>
-    <row r="139" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -2983,7 +2948,7 @@
       <c r="L139" s="4"/>
       <c r="M139" s="4"/>
     </row>
-    <row r="140" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -2998,7 +2963,7 @@
       <c r="L140" s="4"/>
       <c r="M140" s="4"/>
     </row>
-    <row r="141" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -3013,7 +2978,7 @@
       <c r="L141" s="4"/>
       <c r="M141" s="4"/>
     </row>
-    <row r="142" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -3028,7 +2993,7 @@
       <c r="L142" s="4"/>
       <c r="M142" s="4"/>
     </row>
-    <row r="143" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
@@ -3043,7 +3008,7 @@
       <c r="L143" s="4"/>
       <c r="M143" s="4"/>
     </row>
-    <row r="144" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -3058,7 +3023,7 @@
       <c r="L144" s="4"/>
       <c r="M144" s="4"/>
     </row>
-    <row r="145" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -3073,7 +3038,7 @@
       <c r="L145" s="4"/>
       <c r="M145" s="4"/>
     </row>
-    <row r="146" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -3088,7 +3053,7 @@
       <c r="L146" s="4"/>
       <c r="M146" s="4"/>
     </row>
-    <row r="147" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -3103,7 +3068,7 @@
       <c r="L147" s="4"/>
       <c r="M147" s="4"/>
     </row>
-    <row r="148" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -3118,7 +3083,7 @@
       <c r="L148" s="4"/>
       <c r="M148" s="4"/>
     </row>
-    <row r="149" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -3133,7 +3098,7 @@
       <c r="L149" s="4"/>
       <c r="M149" s="4"/>
     </row>
-    <row r="150" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -3148,7 +3113,7 @@
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
     </row>
-    <row r="151" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -3163,7 +3128,7 @@
       <c r="L151" s="4"/>
       <c r="M151" s="4"/>
     </row>
-    <row r="152" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -3178,7 +3143,7 @@
       <c r="L152" s="4"/>
       <c r="M152" s="4"/>
     </row>
-    <row r="153" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
@@ -3193,7 +3158,7 @@
       <c r="L153" s="4"/>
       <c r="M153" s="4"/>
     </row>
-    <row r="154" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4"/>
@@ -3208,7 +3173,7 @@
       <c r="L154" s="4"/>
       <c r="M154" s="4"/>
     </row>
-    <row r="155" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
@@ -3223,7 +3188,7 @@
       <c r="L155" s="4"/>
       <c r="M155" s="4"/>
     </row>
-    <row r="156" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -3238,7 +3203,7 @@
       <c r="L156" s="4"/>
       <c r="M156" s="4"/>
     </row>
-    <row r="157" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -3253,7 +3218,7 @@
       <c r="L157" s="4"/>
       <c r="M157" s="4"/>
     </row>
-    <row r="158" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -3268,7 +3233,7 @@
       <c r="L158" s="4"/>
       <c r="M158" s="4"/>
     </row>
-    <row r="159" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
@@ -3283,7 +3248,7 @@
       <c r="L159" s="4"/>
       <c r="M159" s="4"/>
     </row>
-    <row r="160" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -3298,7 +3263,7 @@
       <c r="L160" s="4"/>
       <c r="M160" s="4"/>
     </row>
-    <row r="161" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -3313,7 +3278,7 @@
       <c r="L161" s="4"/>
       <c r="M161" s="4"/>
     </row>
-    <row r="162" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -3328,7 +3293,7 @@
       <c r="L162" s="4"/>
       <c r="M162" s="4"/>
     </row>
-    <row r="163" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -3343,7 +3308,7 @@
       <c r="L163" s="4"/>
       <c r="M163" s="4"/>
     </row>
-    <row r="164" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -3358,7 +3323,7 @@
       <c r="L164" s="4"/>
       <c r="M164" s="4"/>
     </row>
-    <row r="165" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -3373,7 +3338,7 @@
       <c r="L165" s="4"/>
       <c r="M165" s="4"/>
     </row>
-    <row r="166" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -3388,7 +3353,7 @@
       <c r="L166" s="4"/>
       <c r="M166" s="4"/>
     </row>
-    <row r="167" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -3403,7 +3368,7 @@
       <c r="L167" s="4"/>
       <c r="M167" s="4"/>
     </row>
-    <row r="168" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -3418,7 +3383,7 @@
       <c r="L168" s="4"/>
       <c r="M168" s="4"/>
     </row>
-    <row r="169" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
@@ -3433,7 +3398,7 @@
       <c r="L169" s="4"/>
       <c r="M169" s="4"/>
     </row>
-    <row r="170" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
@@ -3448,7 +3413,7 @@
       <c r="L170" s="4"/>
       <c r="M170" s="4"/>
     </row>
-    <row r="171" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
@@ -3463,7 +3428,7 @@
       <c r="L171" s="4"/>
       <c r="M171" s="4"/>
     </row>
-    <row r="172" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -3478,7 +3443,7 @@
       <c r="L172" s="4"/>
       <c r="M172" s="4"/>
     </row>
-    <row r="173" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -3493,7 +3458,7 @@
       <c r="L173" s="4"/>
       <c r="M173" s="4"/>
     </row>
-    <row r="174" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -3508,7 +3473,7 @@
       <c r="L174" s="4"/>
       <c r="M174" s="4"/>
     </row>
-    <row r="175" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -3523,7 +3488,7 @@
       <c r="L175" s="4"/>
       <c r="M175" s="4"/>
     </row>
-    <row r="176" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -3538,7 +3503,7 @@
       <c r="L176" s="4"/>
       <c r="M176" s="4"/>
     </row>
-    <row r="177" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -3553,7 +3518,7 @@
       <c r="L177" s="4"/>
       <c r="M177" s="4"/>
     </row>
-    <row r="178" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -3568,7 +3533,7 @@
       <c r="L178" s="4"/>
       <c r="M178" s="4"/>
     </row>
-    <row r="179" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
@@ -3583,7 +3548,7 @@
       <c r="L179" s="4"/>
       <c r="M179" s="4"/>
     </row>
-    <row r="180" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -3598,7 +3563,7 @@
       <c r="L180" s="4"/>
       <c r="M180" s="4"/>
     </row>
-    <row r="181" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -3613,7 +3578,7 @@
       <c r="L181" s="4"/>
       <c r="M181" s="4"/>
     </row>
-    <row r="182" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -3628,7 +3593,7 @@
       <c r="L182" s="4"/>
       <c r="M182" s="4"/>
     </row>
-    <row r="183" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -3643,7 +3608,7 @@
       <c r="L183" s="4"/>
       <c r="M183" s="4"/>
     </row>
-    <row r="184" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -3658,7 +3623,7 @@
       <c r="L184" s="4"/>
       <c r="M184" s="4"/>
     </row>
-    <row r="185" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -3673,7 +3638,7 @@
       <c r="L185" s="4"/>
       <c r="M185" s="4"/>
     </row>
-    <row r="186" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
@@ -3688,7 +3653,7 @@
       <c r="L186" s="4"/>
       <c r="M186" s="4"/>
     </row>
-    <row r="187" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
@@ -3703,7 +3668,7 @@
       <c r="L187" s="4"/>
       <c r="M187" s="4"/>
     </row>
-    <row r="188" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
@@ -3718,7 +3683,7 @@
       <c r="L188" s="4"/>
       <c r="M188" s="4"/>
     </row>
-    <row r="189" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -3733,7 +3698,7 @@
       <c r="L189" s="4"/>
       <c r="M189" s="4"/>
     </row>
-    <row r="190" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -3748,7 +3713,7 @@
       <c r="L190" s="4"/>
       <c r="M190" s="4"/>
     </row>
-    <row r="191" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -3763,7 +3728,7 @@
       <c r="L191" s="4"/>
       <c r="M191" s="4"/>
     </row>
-    <row r="192" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -3778,7 +3743,7 @@
       <c r="L192" s="4"/>
       <c r="M192" s="4"/>
     </row>
-    <row r="193" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -3793,7 +3758,7 @@
       <c r="L193" s="4"/>
       <c r="M193" s="4"/>
     </row>
-    <row r="194" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -3808,7 +3773,7 @@
       <c r="L194" s="4"/>
       <c r="M194" s="4"/>
     </row>
-    <row r="195" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -3823,7 +3788,7 @@
       <c r="L195" s="4"/>
       <c r="M195" s="4"/>
     </row>
-    <row r="196" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
@@ -3838,7 +3803,7 @@
       <c r="L196" s="4"/>
       <c r="M196" s="4"/>
     </row>
-    <row r="197" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
       <c r="C197" s="4"/>
@@ -3853,7 +3818,7 @@
       <c r="L197" s="4"/>
       <c r="M197" s="4"/>
     </row>
-    <row r="198" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
@@ -3868,7 +3833,7 @@
       <c r="L198" s="4"/>
       <c r="M198" s="4"/>
     </row>
-    <row r="199" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
@@ -3883,7 +3848,7 @@
       <c r="L199" s="4"/>
       <c r="M199" s="4"/>
     </row>
-    <row r="200" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
@@ -3898,7 +3863,7 @@
       <c r="L200" s="4"/>
       <c r="M200" s="4"/>
     </row>
-    <row r="201" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
@@ -3913,7 +3878,7 @@
       <c r="L201" s="4"/>
       <c r="M201" s="4"/>
     </row>
-    <row r="202" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
@@ -3928,7 +3893,7 @@
       <c r="L202" s="4"/>
       <c r="M202" s="4"/>
     </row>
-    <row r="203" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -3943,7 +3908,7 @@
       <c r="L203" s="4"/>
       <c r="M203" s="4"/>
     </row>
-    <row r="204" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="4"/>
       <c r="B204" s="4"/>
       <c r="C204" s="4"/>
@@ -3958,7 +3923,7 @@
       <c r="L204" s="4"/>
       <c r="M204" s="4"/>
     </row>
-    <row r="205" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="4"/>
       <c r="B205" s="4"/>
       <c r="C205" s="4"/>
@@ -3973,7 +3938,7 @@
       <c r="L205" s="4"/>
       <c r="M205" s="4"/>
     </row>
-    <row r="206" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="4"/>
       <c r="B206" s="4"/>
       <c r="C206" s="4"/>
@@ -3988,7 +3953,7 @@
       <c r="L206" s="4"/>
       <c r="M206" s="4"/>
     </row>
-    <row r="207" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="4"/>
       <c r="B207" s="4"/>
       <c r="C207" s="4"/>
@@ -4003,7 +3968,7 @@
       <c r="L207" s="4"/>
       <c r="M207" s="4"/>
     </row>
-    <row r="208" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="4"/>
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
@@ -4018,7 +3983,7 @@
       <c r="L208" s="4"/>
       <c r="M208" s="4"/>
     </row>
-    <row r="209" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="4"/>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
@@ -4033,7 +3998,7 @@
       <c r="L209" s="4"/>
       <c r="M209" s="4"/>
     </row>
-    <row r="210" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
@@ -4048,7 +4013,7 @@
       <c r="L210" s="4"/>
       <c r="M210" s="4"/>
     </row>
-    <row r="211" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
@@ -4063,7 +4028,7 @@
       <c r="L211" s="4"/>
       <c r="M211" s="4"/>
     </row>
-    <row r="212" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
@@ -4078,7 +4043,7 @@
       <c r="L212" s="4"/>
       <c r="M212" s="4"/>
     </row>
-    <row r="213" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
@@ -4093,7 +4058,7 @@
       <c r="L213" s="4"/>
       <c r="M213" s="4"/>
     </row>
-    <row r="214" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="4"/>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
@@ -4108,7 +4073,7 @@
       <c r="L214" s="4"/>
       <c r="M214" s="4"/>
     </row>
-    <row r="215" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="4"/>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
@@ -4123,7 +4088,7 @@
       <c r="L215" s="4"/>
       <c r="M215" s="4"/>
     </row>
-    <row r="216" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="4"/>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
@@ -4138,7 +4103,7 @@
       <c r="L216" s="4"/>
       <c r="M216" s="4"/>
     </row>
-    <row r="217" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
@@ -4153,7 +4118,7 @@
       <c r="L217" s="4"/>
       <c r="M217" s="4"/>
     </row>
-    <row r="218" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="4"/>
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
@@ -4168,7 +4133,7 @@
       <c r="L218" s="4"/>
       <c r="M218" s="4"/>
     </row>
-    <row r="219" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="4"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
@@ -4183,7 +4148,7 @@
       <c r="L219" s="4"/>
       <c r="M219" s="4"/>
     </row>
-    <row r="220" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="4"/>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
@@ -4198,7 +4163,7 @@
       <c r="L220" s="4"/>
       <c r="M220" s="4"/>
     </row>
-    <row r="221" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="4"/>
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
@@ -4213,7 +4178,7 @@
       <c r="L221" s="4"/>
       <c r="M221" s="4"/>
     </row>
-    <row r="222" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="4"/>
       <c r="B222" s="4"/>
       <c r="C222" s="4"/>
@@ -4228,7 +4193,7 @@
       <c r="L222" s="4"/>
       <c r="M222" s="4"/>
     </row>
-    <row r="223" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="4"/>
       <c r="B223" s="4"/>
       <c r="C223" s="4"/>
@@ -4243,7 +4208,7 @@
       <c r="L223" s="4"/>
       <c r="M223" s="4"/>
     </row>
-    <row r="224" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="4"/>
       <c r="B224" s="4"/>
       <c r="C224" s="4"/>
@@ -4258,7 +4223,7 @@
       <c r="L224" s="4"/>
       <c r="M224" s="4"/>
     </row>
-    <row r="225" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="4"/>
       <c r="B225" s="4"/>
       <c r="C225" s="4"/>
@@ -4273,7 +4238,7 @@
       <c r="L225" s="4"/>
       <c r="M225" s="4"/>
     </row>
-    <row r="226" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="4"/>
       <c r="B226" s="4"/>
       <c r="C226" s="4"/>
@@ -4288,7 +4253,7 @@
       <c r="L226" s="4"/>
       <c r="M226" s="4"/>
     </row>
-    <row r="227" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="4"/>
       <c r="B227" s="4"/>
       <c r="C227" s="4"/>
@@ -4303,7 +4268,7 @@
       <c r="L227" s="4"/>
       <c r="M227" s="4"/>
     </row>
-    <row r="228" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
@@ -4318,7 +4283,7 @@
       <c r="L228" s="4"/>
       <c r="M228" s="4"/>
     </row>
-    <row r="229" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="4"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
@@ -4333,7 +4298,7 @@
       <c r="L229" s="4"/>
       <c r="M229" s="4"/>
     </row>
-    <row r="230" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
@@ -4348,7 +4313,7 @@
       <c r="L230" s="4"/>
       <c r="M230" s="4"/>
     </row>
-    <row r="231" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
@@ -4363,7 +4328,7 @@
       <c r="L231" s="4"/>
       <c r="M231" s="4"/>
     </row>
-    <row r="232" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
@@ -4378,7 +4343,7 @@
       <c r="L232" s="4"/>
       <c r="M232" s="4"/>
     </row>
-    <row r="233" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
@@ -4393,7 +4358,7 @@
       <c r="L233" s="4"/>
       <c r="M233" s="4"/>
     </row>
-    <row r="234" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="4"/>
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
@@ -4408,7 +4373,7 @@
       <c r="L234" s="4"/>
       <c r="M234" s="4"/>
     </row>
-    <row r="235" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
@@ -4423,7 +4388,7 @@
       <c r="L235" s="4"/>
       <c r="M235" s="4"/>
     </row>
-    <row r="236" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
@@ -4438,7 +4403,7 @@
       <c r="L236" s="4"/>
       <c r="M236" s="4"/>
     </row>
-    <row r="237" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
@@ -4453,7 +4418,7 @@
       <c r="L237" s="4"/>
       <c r="M237" s="4"/>
     </row>
-    <row r="238" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
@@ -4468,7 +4433,7 @@
       <c r="L238" s="4"/>
       <c r="M238" s="4"/>
     </row>
-    <row r="239" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
@@ -4483,7 +4448,7 @@
       <c r="L239" s="4"/>
       <c r="M239" s="4"/>
     </row>
-    <row r="240" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
@@ -4498,7 +4463,7 @@
       <c r="L240" s="4"/>
       <c r="M240" s="4"/>
     </row>
-    <row r="241" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="4"/>
       <c r="B241" s="4"/>
       <c r="C241" s="4"/>
@@ -4513,7 +4478,7 @@
       <c r="L241" s="4"/>
       <c r="M241" s="4"/>
     </row>
-    <row r="242" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="4"/>
       <c r="B242" s="4"/>
       <c r="C242" s="4"/>
@@ -4528,7 +4493,7 @@
       <c r="L242" s="4"/>
       <c r="M242" s="4"/>
     </row>
-    <row r="243" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="4"/>
       <c r="B243" s="4"/>
       <c r="C243" s="4"/>
@@ -4543,7 +4508,7 @@
       <c r="L243" s="4"/>
       <c r="M243" s="4"/>
     </row>
-    <row r="244" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="4"/>
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
@@ -4558,7 +4523,7 @@
       <c r="L244" s="4"/>
       <c r="M244" s="4"/>
     </row>
-    <row r="245" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="4"/>
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
@@ -4573,7 +4538,7 @@
       <c r="L245" s="4"/>
       <c r="M245" s="4"/>
     </row>
-    <row r="246" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="4"/>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
@@ -4588,7 +4553,7 @@
       <c r="L246" s="4"/>
       <c r="M246" s="4"/>
     </row>
-    <row r="247" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="4"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
@@ -4603,7 +4568,7 @@
       <c r="L247" s="4"/>
       <c r="M247" s="4"/>
     </row>
-    <row r="248" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
@@ -4618,7 +4583,7 @@
       <c r="L248" s="4"/>
       <c r="M248" s="4"/>
     </row>
-    <row r="249" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
@@ -4633,7 +4598,7 @@
       <c r="L249" s="4"/>
       <c r="M249" s="4"/>
     </row>
-    <row r="250" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="4"/>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
@@ -4648,7 +4613,7 @@
       <c r="L250" s="4"/>
       <c r="M250" s="4"/>
     </row>
-    <row r="251" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="4"/>
       <c r="B251" s="4"/>
       <c r="C251" s="4"/>
@@ -4663,7 +4628,7 @@
       <c r="L251" s="4"/>
       <c r="M251" s="4"/>
     </row>
-    <row r="252" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="4"/>
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
@@ -4678,7 +4643,7 @@
       <c r="L252" s="4"/>
       <c r="M252" s="4"/>
     </row>
-    <row r="253" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="4"/>
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
@@ -4693,7 +4658,7 @@
       <c r="L253" s="4"/>
       <c r="M253" s="4"/>
     </row>
-    <row r="254" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="4"/>
       <c r="B254" s="4"/>
       <c r="C254" s="4"/>
@@ -4708,7 +4673,7 @@
       <c r="L254" s="4"/>
       <c r="M254" s="4"/>
     </row>
-    <row r="255" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="4"/>
       <c r="B255" s="4"/>
       <c r="C255" s="4"/>
@@ -4723,7 +4688,7 @@
       <c r="L255" s="4"/>
       <c r="M255" s="4"/>
     </row>
-    <row r="256" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="4"/>
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
@@ -4738,7 +4703,7 @@
       <c r="L256" s="4"/>
       <c r="M256" s="4"/>
     </row>
-    <row r="257" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="4"/>
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
@@ -4753,7 +4718,7 @@
       <c r="L257" s="4"/>
       <c r="M257" s="4"/>
     </row>
-    <row r="258" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="4"/>
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
@@ -4768,7 +4733,7 @@
       <c r="L258" s="4"/>
       <c r="M258" s="4"/>
     </row>
-    <row r="259" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="4"/>
       <c r="B259" s="4"/>
       <c r="C259" s="4"/>
@@ -4783,7 +4748,7 @@
       <c r="L259" s="4"/>
       <c r="M259" s="4"/>
     </row>
-    <row r="260" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="4"/>
       <c r="B260" s="4"/>
       <c r="C260" s="4"/>
@@ -4798,7 +4763,7 @@
       <c r="L260" s="4"/>
       <c r="M260" s="4"/>
     </row>
-    <row r="261" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="4"/>
       <c r="B261" s="4"/>
       <c r="C261" s="4"/>
@@ -4813,7 +4778,7 @@
       <c r="L261" s="4"/>
       <c r="M261" s="4"/>
     </row>
-    <row r="262" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="4"/>
       <c r="B262" s="4"/>
       <c r="C262" s="4"/>
@@ -4828,7 +4793,7 @@
       <c r="L262" s="4"/>
       <c r="M262" s="4"/>
     </row>
-    <row r="263" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="4"/>
       <c r="B263" s="4"/>
       <c r="C263" s="4"/>
@@ -4843,7 +4808,7 @@
       <c r="L263" s="4"/>
       <c r="M263" s="4"/>
     </row>
-    <row r="264" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="4"/>
       <c r="B264" s="4"/>
       <c r="C264" s="4"/>
@@ -4858,7 +4823,7 @@
       <c r="L264" s="4"/>
       <c r="M264" s="4"/>
     </row>
-    <row r="265" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="4"/>
       <c r="B265" s="4"/>
       <c r="C265" s="4"/>
@@ -4873,7 +4838,7 @@
       <c r="L265" s="4"/>
       <c r="M265" s="4"/>
     </row>
-    <row r="266" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="4"/>
       <c r="B266" s="4"/>
       <c r="C266" s="4"/>
@@ -4888,7 +4853,7 @@
       <c r="L266" s="4"/>
       <c r="M266" s="4"/>
     </row>
-    <row r="267" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
@@ -4903,7 +4868,7 @@
       <c r="L267" s="4"/>
       <c r="M267" s="4"/>
     </row>
-    <row r="268" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="4"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
@@ -4918,7 +4883,7 @@
       <c r="L268" s="4"/>
       <c r="M268" s="4"/>
     </row>
-    <row r="269" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
@@ -4933,7 +4898,7 @@
       <c r="L269" s="4"/>
       <c r="M269" s="4"/>
     </row>
-    <row r="270" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
@@ -4948,7 +4913,7 @@
       <c r="L270" s="4"/>
       <c r="M270" s="4"/>
     </row>
-    <row r="271" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
@@ -4963,7 +4928,7 @@
       <c r="L271" s="4"/>
       <c r="M271" s="4"/>
     </row>
-    <row r="272" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
@@ -4978,7 +4943,7 @@
       <c r="L272" s="4"/>
       <c r="M272" s="4"/>
     </row>
-    <row r="273" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="4"/>
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
@@ -4993,7 +4958,7 @@
       <c r="L273" s="4"/>
       <c r="M273" s="4"/>
     </row>
-    <row r="274" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
@@ -5008,7 +4973,7 @@
       <c r="L274" s="4"/>
       <c r="M274" s="4"/>
     </row>
-    <row r="275" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="4"/>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
@@ -5023,7 +4988,7 @@
       <c r="L275" s="4"/>
       <c r="M275" s="4"/>
     </row>
-    <row r="276" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="4"/>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
@@ -5038,7 +5003,7 @@
       <c r="L276" s="4"/>
       <c r="M276" s="4"/>
     </row>
-    <row r="277" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="4"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
@@ -5053,7 +5018,7 @@
       <c r="L277" s="4"/>
       <c r="M277" s="4"/>
     </row>
-    <row r="278" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="4"/>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
@@ -5068,7 +5033,7 @@
       <c r="L278" s="4"/>
       <c r="M278" s="4"/>
     </row>
-    <row r="279" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
@@ -5083,7 +5048,7 @@
       <c r="L279" s="4"/>
       <c r="M279" s="4"/>
     </row>
-    <row r="280" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="4"/>
       <c r="B280" s="4"/>
       <c r="C280" s="4"/>
@@ -5098,7 +5063,7 @@
       <c r="L280" s="4"/>
       <c r="M280" s="4"/>
     </row>
-    <row r="281" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="4"/>
       <c r="B281" s="4"/>
       <c r="C281" s="4"/>
@@ -5113,7 +5078,7 @@
       <c r="L281" s="4"/>
       <c r="M281" s="4"/>
     </row>
-    <row r="282" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="4"/>
       <c r="B282" s="4"/>
       <c r="C282" s="4"/>
@@ -5128,7 +5093,7 @@
       <c r="L282" s="4"/>
       <c r="M282" s="4"/>
     </row>
-    <row r="283" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="4"/>
       <c r="B283" s="4"/>
       <c r="C283" s="4"/>
@@ -5143,7 +5108,7 @@
       <c r="L283" s="4"/>
       <c r="M283" s="4"/>
     </row>
-    <row r="284" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="4"/>
       <c r="B284" s="4"/>
       <c r="C284" s="4"/>
@@ -5158,7 +5123,7 @@
       <c r="L284" s="4"/>
       <c r="M284" s="4"/>
     </row>
-    <row r="285" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="4"/>
       <c r="B285" s="4"/>
       <c r="C285" s="4"/>
@@ -5173,7 +5138,7 @@
       <c r="L285" s="4"/>
       <c r="M285" s="4"/>
     </row>
-    <row r="286" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
@@ -5188,7 +5153,7 @@
       <c r="L286" s="4"/>
       <c r="M286" s="4"/>
     </row>
-    <row r="287" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
@@ -5203,7 +5168,7 @@
       <c r="L287" s="4"/>
       <c r="M287" s="4"/>
     </row>
-    <row r="288" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
@@ -5218,7 +5183,7 @@
       <c r="L288" s="4"/>
       <c r="M288" s="4"/>
     </row>
-    <row r="289" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="4"/>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
@@ -5233,7 +5198,7 @@
       <c r="L289" s="4"/>
       <c r="M289" s="4"/>
     </row>
-    <row r="290" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="4"/>
       <c r="B290" s="4"/>
       <c r="C290" s="4"/>
@@ -5248,7 +5213,7 @@
       <c r="L290" s="4"/>
       <c r="M290" s="4"/>
     </row>
-    <row r="291" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="4"/>
       <c r="B291" s="4"/>
       <c r="C291" s="4"/>
@@ -5263,7 +5228,7 @@
       <c r="L291" s="4"/>
       <c r="M291" s="4"/>
     </row>
-    <row r="292" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="4"/>
       <c r="B292" s="4"/>
       <c r="C292" s="4"/>
@@ -5278,7 +5243,7 @@
       <c r="L292" s="4"/>
       <c r="M292" s="4"/>
     </row>
-    <row r="293" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="4"/>
       <c r="B293" s="4"/>
       <c r="C293" s="4"/>
@@ -5293,7 +5258,7 @@
       <c r="L293" s="4"/>
       <c r="M293" s="4"/>
     </row>
-    <row r="294" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="4"/>
       <c r="B294" s="4"/>
       <c r="C294" s="4"/>
@@ -5308,7 +5273,7 @@
       <c r="L294" s="4"/>
       <c r="M294" s="4"/>
     </row>
-    <row r="295" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="4"/>
       <c r="B295" s="4"/>
       <c r="C295" s="4"/>
@@ -5323,7 +5288,7 @@
       <c r="L295" s="4"/>
       <c r="M295" s="4"/>
     </row>
-    <row r="296" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="4"/>
       <c r="B296" s="4"/>
       <c r="C296" s="4"/>
@@ -5338,7 +5303,7 @@
       <c r="L296" s="4"/>
       <c r="M296" s="4"/>
     </row>
-    <row r="297" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="4"/>
       <c r="B297" s="4"/>
       <c r="C297" s="4"/>
@@ -5353,7 +5318,7 @@
       <c r="L297" s="4"/>
       <c r="M297" s="4"/>
     </row>
-    <row r="298" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="4"/>
       <c r="B298" s="4"/>
       <c r="C298" s="4"/>
@@ -5368,7 +5333,7 @@
       <c r="L298" s="4"/>
       <c r="M298" s="4"/>
     </row>
-    <row r="299" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="4"/>
       <c r="B299" s="4"/>
       <c r="C299" s="4"/>
@@ -5383,7 +5348,7 @@
       <c r="L299" s="4"/>
       <c r="M299" s="4"/>
     </row>
-    <row r="300" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="4"/>
       <c r="B300" s="4"/>
       <c r="C300" s="4"/>
@@ -5398,7 +5363,7 @@
       <c r="L300" s="4"/>
       <c r="M300" s="4"/>
     </row>
-    <row r="301" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="4"/>
       <c r="B301" s="4"/>
       <c r="C301" s="4"/>
@@ -5413,7 +5378,7 @@
       <c r="L301" s="4"/>
       <c r="M301" s="4"/>
     </row>
-    <row r="302" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="4"/>
       <c r="B302" s="4"/>
       <c r="C302" s="4"/>
@@ -5428,7 +5393,7 @@
       <c r="L302" s="4"/>
       <c r="M302" s="4"/>
     </row>
-    <row r="303" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="4"/>
       <c r="B303" s="4"/>
       <c r="C303" s="4"/>
@@ -5443,7 +5408,7 @@
       <c r="L303" s="4"/>
       <c r="M303" s="4"/>
     </row>
-    <row r="304" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="4"/>
       <c r="B304" s="4"/>
       <c r="C304" s="4"/>
@@ -5458,7 +5423,7 @@
       <c r="L304" s="4"/>
       <c r="M304" s="4"/>
     </row>
-    <row r="305" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="4"/>
       <c r="B305" s="4"/>
       <c r="C305" s="4"/>
@@ -5473,7 +5438,7 @@
       <c r="L305" s="4"/>
       <c r="M305" s="4"/>
     </row>
-    <row r="306" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
@@ -5488,7 +5453,7 @@
       <c r="L306" s="4"/>
       <c r="M306" s="4"/>
     </row>
-    <row r="307" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
@@ -5503,7 +5468,7 @@
       <c r="L307" s="4"/>
       <c r="M307" s="4"/>
     </row>
-    <row r="308" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
@@ -5518,7 +5483,7 @@
       <c r="L308" s="4"/>
       <c r="M308" s="4"/>
     </row>
-    <row r="309" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
@@ -5533,7 +5498,7 @@
       <c r="L309" s="4"/>
       <c r="M309" s="4"/>
     </row>
-    <row r="310" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
@@ -5548,7 +5513,7 @@
       <c r="L310" s="4"/>
       <c r="M310" s="4"/>
     </row>
-    <row r="311" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="4"/>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
@@ -5563,7 +5528,7 @@
       <c r="L311" s="4"/>
       <c r="M311" s="4"/>
     </row>
-    <row r="312" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="4"/>
       <c r="B312" s="4"/>
       <c r="C312" s="4"/>
@@ -5578,7 +5543,7 @@
       <c r="L312" s="4"/>
       <c r="M312" s="4"/>
     </row>
-    <row r="313" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
@@ -5593,7 +5558,7 @@
       <c r="L313" s="4"/>
       <c r="M313" s="4"/>
     </row>
-    <row r="314" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
@@ -5608,7 +5573,7 @@
       <c r="L314" s="4"/>
       <c r="M314" s="4"/>
     </row>
-    <row r="315" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
@@ -5623,7 +5588,7 @@
       <c r="L315" s="4"/>
       <c r="M315" s="4"/>
     </row>
-    <row r="316" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
@@ -5638,7 +5603,7 @@
       <c r="L316" s="4"/>
       <c r="M316" s="4"/>
     </row>
-    <row r="317" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
@@ -5653,7 +5618,7 @@
       <c r="L317" s="4"/>
       <c r="M317" s="4"/>
     </row>
-    <row r="318" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
@@ -5668,7 +5633,7 @@
       <c r="L318" s="4"/>
       <c r="M318" s="4"/>
     </row>
-    <row r="319" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="4"/>
       <c r="B319" s="4"/>
       <c r="C319" s="4"/>
@@ -5683,7 +5648,7 @@
       <c r="L319" s="4"/>
       <c r="M319" s="4"/>
     </row>
-    <row r="320" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="4"/>
       <c r="B320" s="4"/>
       <c r="C320" s="4"/>
@@ -5698,7 +5663,7 @@
       <c r="L320" s="4"/>
       <c r="M320" s="4"/>
     </row>
-    <row r="321" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="4"/>
       <c r="B321" s="4"/>
       <c r="C321" s="4"/>
@@ -5713,7 +5678,7 @@
       <c r="L321" s="4"/>
       <c r="M321" s="4"/>
     </row>
-    <row r="322" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="4"/>
       <c r="B322" s="4"/>
       <c r="C322" s="4"/>
@@ -5728,7 +5693,7 @@
       <c r="L322" s="4"/>
       <c r="M322" s="4"/>
     </row>
-    <row r="323" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="4"/>
       <c r="B323" s="4"/>
       <c r="C323" s="4"/>
@@ -5743,7 +5708,7 @@
       <c r="L323" s="4"/>
       <c r="M323" s="4"/>
     </row>
-    <row r="324" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="4"/>
       <c r="B324" s="4"/>
       <c r="C324" s="4"/>
@@ -5758,7 +5723,7 @@
       <c r="L324" s="4"/>
       <c r="M324" s="4"/>
     </row>
-    <row r="325" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
@@ -5773,7 +5738,7 @@
       <c r="L325" s="4"/>
       <c r="M325" s="4"/>
     </row>
-    <row r="326" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
@@ -5788,7 +5753,7 @@
       <c r="L326" s="4"/>
       <c r="M326" s="4"/>
     </row>
-    <row r="327" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
@@ -5803,7 +5768,7 @@
       <c r="L327" s="4"/>
       <c r="M327" s="4"/>
     </row>
-    <row r="328" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
@@ -5818,7 +5783,7 @@
       <c r="L328" s="4"/>
       <c r="M328" s="4"/>
     </row>
-    <row r="329" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="4"/>
       <c r="B329" s="4"/>
       <c r="C329" s="4"/>
@@ -5833,7 +5798,7 @@
       <c r="L329" s="4"/>
       <c r="M329" s="4"/>
     </row>
-    <row r="330" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="4"/>
       <c r="B330" s="4"/>
       <c r="C330" s="4"/>
@@ -5848,7 +5813,7 @@
       <c r="L330" s="4"/>
       <c r="M330" s="4"/>
     </row>
-    <row r="331" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="4"/>
       <c r="B331" s="4"/>
       <c r="C331" s="4"/>
@@ -5863,7 +5828,7 @@
       <c r="L331" s="4"/>
       <c r="M331" s="4"/>
     </row>
-    <row r="332" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="4"/>
       <c r="B332" s="4"/>
       <c r="C332" s="4"/>
@@ -5878,7 +5843,7 @@
       <c r="L332" s="4"/>
       <c r="M332" s="4"/>
     </row>
-    <row r="333" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="4"/>
       <c r="B333" s="4"/>
       <c r="C333" s="4"/>
@@ -5893,7 +5858,7 @@
       <c r="L333" s="4"/>
       <c r="M333" s="4"/>
     </row>
-    <row r="334" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="4"/>
       <c r="B334" s="4"/>
       <c r="C334" s="4"/>
@@ -5908,7 +5873,7 @@
       <c r="L334" s="4"/>
       <c r="M334" s="4"/>
     </row>
-    <row r="335" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="4"/>
       <c r="B335" s="4"/>
       <c r="C335" s="4"/>
@@ -5923,7 +5888,7 @@
       <c r="L335" s="4"/>
       <c r="M335" s="4"/>
     </row>
-    <row r="336" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="4"/>
       <c r="B336" s="4"/>
       <c r="C336" s="4"/>
@@ -5938,7 +5903,7 @@
       <c r="L336" s="4"/>
       <c r="M336" s="4"/>
     </row>
-    <row r="337" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="4"/>
       <c r="B337" s="4"/>
       <c r="C337" s="4"/>
@@ -5953,7 +5918,7 @@
       <c r="L337" s="4"/>
       <c r="M337" s="4"/>
     </row>
-    <row r="338" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="4"/>
       <c r="B338" s="4"/>
       <c r="C338" s="4"/>
@@ -5968,7 +5933,7 @@
       <c r="L338" s="4"/>
       <c r="M338" s="4"/>
     </row>
-    <row r="339" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="4"/>
       <c r="B339" s="4"/>
       <c r="C339" s="4"/>
@@ -5983,7 +5948,7 @@
       <c r="L339" s="4"/>
       <c r="M339" s="4"/>
     </row>
-    <row r="340" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="4"/>
       <c r="B340" s="4"/>
       <c r="C340" s="4"/>
@@ -5998,7 +5963,7 @@
       <c r="L340" s="4"/>
       <c r="M340" s="4"/>
     </row>
-    <row r="341" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="4"/>
       <c r="B341" s="4"/>
       <c r="C341" s="4"/>
@@ -6013,7 +5978,7 @@
       <c r="L341" s="4"/>
       <c r="M341" s="4"/>
     </row>
-    <row r="342" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="4"/>
       <c r="B342" s="4"/>
       <c r="C342" s="4"/>
@@ -6028,7 +5993,7 @@
       <c r="L342" s="4"/>
       <c r="M342" s="4"/>
     </row>
-    <row r="343" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="4"/>
       <c r="B343" s="4"/>
       <c r="C343" s="4"/>
@@ -6043,7 +6008,7 @@
       <c r="L343" s="4"/>
       <c r="M343" s="4"/>
     </row>
-    <row r="344" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="4"/>
       <c r="B344" s="4"/>
       <c r="C344" s="4"/>
@@ -6058,7 +6023,7 @@
       <c r="L344" s="4"/>
       <c r="M344" s="4"/>
     </row>
-    <row r="345" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="4"/>
       <c r="B345" s="4"/>
       <c r="C345" s="4"/>
@@ -6073,7 +6038,7 @@
       <c r="L345" s="4"/>
       <c r="M345" s="4"/>
     </row>
-    <row r="346" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="4"/>
       <c r="B346" s="4"/>
       <c r="C346" s="4"/>
@@ -6088,7 +6053,7 @@
       <c r="L346" s="4"/>
       <c r="M346" s="4"/>
     </row>
-    <row r="347" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="4"/>
       <c r="B347" s="4"/>
       <c r="C347" s="4"/>
@@ -6103,7 +6068,7 @@
       <c r="L347" s="4"/>
       <c r="M347" s="4"/>
     </row>
-    <row r="348" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="4"/>
       <c r="B348" s="4"/>
       <c r="C348" s="4"/>
@@ -6118,7 +6083,7 @@
       <c r="L348" s="4"/>
       <c r="M348" s="4"/>
     </row>
-    <row r="349" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="4"/>
       <c r="B349" s="4"/>
       <c r="C349" s="4"/>
@@ -6133,7 +6098,7 @@
       <c r="L349" s="4"/>
       <c r="M349" s="4"/>
     </row>
-    <row r="350" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="4"/>
       <c r="B350" s="4"/>
       <c r="C350" s="4"/>
@@ -6148,7 +6113,7 @@
       <c r="L350" s="4"/>
       <c r="M350" s="4"/>
     </row>
-    <row r="351" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="4"/>
       <c r="B351" s="4"/>
       <c r="C351" s="4"/>
@@ -6163,7 +6128,7 @@
       <c r="L351" s="4"/>
       <c r="M351" s="4"/>
     </row>
-    <row r="352" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="4"/>
       <c r="B352" s="4"/>
       <c r="C352" s="4"/>
@@ -6178,7 +6143,7 @@
       <c r="L352" s="4"/>
       <c r="M352" s="4"/>
     </row>
-    <row r="353" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
@@ -6193,7 +6158,7 @@
       <c r="L353" s="4"/>
       <c r="M353" s="4"/>
     </row>
-    <row r="354" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="4"/>
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
@@ -6208,7 +6173,7 @@
       <c r="L354" s="4"/>
       <c r="M354" s="4"/>
     </row>
-    <row r="355" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="4"/>
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
@@ -6223,7 +6188,7 @@
       <c r="L355" s="4"/>
       <c r="M355" s="4"/>
     </row>
-    <row r="356" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="4"/>
       <c r="B356" s="4"/>
       <c r="C356" s="4"/>
@@ -6238,7 +6203,7 @@
       <c r="L356" s="4"/>
       <c r="M356" s="4"/>
     </row>
-    <row r="357" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="4"/>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
@@ -6253,7 +6218,7 @@
       <c r="L357" s="4"/>
       <c r="M357" s="4"/>
     </row>
-    <row r="358" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="4"/>
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
@@ -6268,7 +6233,7 @@
       <c r="L358" s="4"/>
       <c r="M358" s="4"/>
     </row>
-    <row r="359" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="4"/>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
@@ -6283,7 +6248,7 @@
       <c r="L359" s="4"/>
       <c r="M359" s="4"/>
     </row>
-    <row r="360" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="4"/>
       <c r="B360" s="4"/>
       <c r="C360" s="4"/>
@@ -6298,7 +6263,7 @@
       <c r="L360" s="4"/>
       <c r="M360" s="4"/>
     </row>
-    <row r="361" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="4"/>
       <c r="B361" s="4"/>
       <c r="C361" s="4"/>
@@ -6313,7 +6278,7 @@
       <c r="L361" s="4"/>
       <c r="M361" s="4"/>
     </row>
-    <row r="362" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="4"/>
       <c r="B362" s="4"/>
       <c r="C362" s="4"/>
@@ -6328,7 +6293,7 @@
       <c r="L362" s="4"/>
       <c r="M362" s="4"/>
     </row>
-    <row r="363" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="4"/>
       <c r="B363" s="4"/>
       <c r="C363" s="4"/>
@@ -6343,7 +6308,7 @@
       <c r="L363" s="4"/>
       <c r="M363" s="4"/>
     </row>
-    <row r="364" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="4"/>
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
@@ -6358,7 +6323,7 @@
       <c r="L364" s="4"/>
       <c r="M364" s="4"/>
     </row>
-    <row r="365" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="4"/>
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
@@ -6373,7 +6338,7 @@
       <c r="L365" s="4"/>
       <c r="M365" s="4"/>
     </row>
-    <row r="366" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="4"/>
       <c r="B366" s="4"/>
       <c r="C366" s="4"/>
@@ -6388,7 +6353,7 @@
       <c r="L366" s="4"/>
       <c r="M366" s="4"/>
     </row>
-    <row r="367" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="4"/>
       <c r="B367" s="4"/>
       <c r="C367" s="4"/>
@@ -6403,7 +6368,7 @@
       <c r="L367" s="4"/>
       <c r="M367" s="4"/>
     </row>
-    <row r="368" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="4"/>
       <c r="B368" s="4"/>
       <c r="C368" s="4"/>
@@ -6418,7 +6383,7 @@
       <c r="L368" s="4"/>
       <c r="M368" s="4"/>
     </row>
-    <row r="369" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="4"/>
       <c r="B369" s="4"/>
       <c r="C369" s="4"/>
@@ -6433,7 +6398,7 @@
       <c r="L369" s="4"/>
       <c r="M369" s="4"/>
     </row>
-    <row r="370" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="4"/>
       <c r="B370" s="4"/>
       <c r="C370" s="4"/>
@@ -6448,7 +6413,7 @@
       <c r="L370" s="4"/>
       <c r="M370" s="4"/>
     </row>
-    <row r="371" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="4"/>
       <c r="B371" s="4"/>
       <c r="C371" s="4"/>
@@ -6463,7 +6428,7 @@
       <c r="L371" s="4"/>
       <c r="M371" s="4"/>
     </row>
-    <row r="372" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="4"/>
       <c r="B372" s="4"/>
       <c r="C372" s="4"/>
@@ -6478,7 +6443,7 @@
       <c r="L372" s="4"/>
       <c r="M372" s="4"/>
     </row>
-    <row r="373" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="4"/>
       <c r="B373" s="4"/>
       <c r="C373" s="4"/>
@@ -6493,7 +6458,7 @@
       <c r="L373" s="4"/>
       <c r="M373" s="4"/>
     </row>
-    <row r="374" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="4"/>
       <c r="B374" s="4"/>
       <c r="C374" s="4"/>
@@ -6508,7 +6473,7 @@
       <c r="L374" s="4"/>
       <c r="M374" s="4"/>
     </row>
-    <row r="375" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="4"/>
       <c r="B375" s="4"/>
       <c r="C375" s="4"/>
@@ -6523,7 +6488,7 @@
       <c r="L375" s="4"/>
       <c r="M375" s="4"/>
     </row>
-    <row r="376" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="4"/>
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
@@ -6538,7 +6503,7 @@
       <c r="L376" s="4"/>
       <c r="M376" s="4"/>
     </row>
-    <row r="377" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="4"/>
       <c r="B377" s="4"/>
       <c r="C377" s="4"/>
@@ -6553,7 +6518,7 @@
       <c r="L377" s="4"/>
       <c r="M377" s="4"/>
     </row>
-    <row r="378" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="4"/>
       <c r="B378" s="4"/>
       <c r="C378" s="4"/>
@@ -6568,7 +6533,7 @@
       <c r="L378" s="4"/>
       <c r="M378" s="4"/>
     </row>
-    <row r="379" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="4"/>
       <c r="B379" s="4"/>
       <c r="C379" s="4"/>
@@ -6583,7 +6548,7 @@
       <c r="L379" s="4"/>
       <c r="M379" s="4"/>
     </row>
-    <row r="380" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="4"/>
       <c r="B380" s="4"/>
       <c r="C380" s="4"/>
@@ -6598,7 +6563,7 @@
       <c r="L380" s="4"/>
       <c r="M380" s="4"/>
     </row>
-    <row r="381" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="4"/>
       <c r="B381" s="4"/>
       <c r="C381" s="4"/>
@@ -6613,7 +6578,7 @@
       <c r="L381" s="4"/>
       <c r="M381" s="4"/>
     </row>
-    <row r="382" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="4"/>
       <c r="B382" s="4"/>
       <c r="C382" s="4"/>
@@ -6628,7 +6593,7 @@
       <c r="L382" s="4"/>
       <c r="M382" s="4"/>
     </row>
-    <row r="383" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="4"/>
       <c r="B383" s="4"/>
       <c r="C383" s="4"/>
@@ -6643,7 +6608,7 @@
       <c r="L383" s="4"/>
       <c r="M383" s="4"/>
     </row>
-    <row r="384" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="4"/>
       <c r="B384" s="4"/>
       <c r="C384" s="4"/>
@@ -6658,7 +6623,7 @@
       <c r="L384" s="4"/>
       <c r="M384" s="4"/>
     </row>
-    <row r="385" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="4"/>
       <c r="B385" s="4"/>
       <c r="C385" s="4"/>
@@ -6673,7 +6638,7 @@
       <c r="L385" s="4"/>
       <c r="M385" s="4"/>
     </row>
-    <row r="386" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="4"/>
       <c r="B386" s="4"/>
       <c r="C386" s="4"/>
@@ -6688,7 +6653,7 @@
       <c r="L386" s="4"/>
       <c r="M386" s="4"/>
     </row>
-    <row r="387" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="4"/>
       <c r="B387" s="4"/>
       <c r="C387" s="4"/>
@@ -6703,7 +6668,7 @@
       <c r="L387" s="4"/>
       <c r="M387" s="4"/>
     </row>
-    <row r="388" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="4"/>
       <c r="B388" s="4"/>
       <c r="C388" s="4"/>
@@ -6718,7 +6683,7 @@
       <c r="L388" s="4"/>
       <c r="M388" s="4"/>
     </row>
-    <row r="389" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="4"/>
       <c r="B389" s="4"/>
       <c r="C389" s="4"/>
@@ -6733,7 +6698,7 @@
       <c r="L389" s="4"/>
       <c r="M389" s="4"/>
     </row>
-    <row r="390" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="4"/>
       <c r="B390" s="4"/>
       <c r="C390" s="4"/>
@@ -6748,7 +6713,7 @@
       <c r="L390" s="4"/>
       <c r="M390" s="4"/>
     </row>
-    <row r="391" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="4"/>
       <c r="B391" s="4"/>
       <c r="C391" s="4"/>
@@ -6763,7 +6728,7 @@
       <c r="L391" s="4"/>
       <c r="M391" s="4"/>
     </row>
-    <row r="392" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="4"/>
       <c r="B392" s="4"/>
       <c r="C392" s="4"/>
@@ -6778,7 +6743,7 @@
       <c r="L392" s="4"/>
       <c r="M392" s="4"/>
     </row>
-    <row r="393" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="4"/>
       <c r="B393" s="4"/>
       <c r="C393" s="4"/>
@@ -6793,7 +6758,7 @@
       <c r="L393" s="4"/>
       <c r="M393" s="4"/>
     </row>
-    <row r="394" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="4"/>
       <c r="B394" s="4"/>
       <c r="C394" s="4"/>
@@ -6808,7 +6773,7 @@
       <c r="L394" s="4"/>
       <c r="M394" s="4"/>
     </row>
-    <row r="395" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="4"/>
       <c r="B395" s="4"/>
       <c r="C395" s="4"/>
@@ -6823,7 +6788,7 @@
       <c r="L395" s="4"/>
       <c r="M395" s="4"/>
     </row>
-    <row r="396" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="4"/>
       <c r="B396" s="4"/>
       <c r="C396" s="4"/>
@@ -6838,7 +6803,7 @@
       <c r="L396" s="4"/>
       <c r="M396" s="4"/>
     </row>
-    <row r="397" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="4"/>
       <c r="B397" s="4"/>
       <c r="C397" s="4"/>
@@ -6853,7 +6818,7 @@
       <c r="L397" s="4"/>
       <c r="M397" s="4"/>
     </row>
-    <row r="398" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="4"/>
       <c r="B398" s="4"/>
       <c r="C398" s="4"/>
@@ -6868,7 +6833,7 @@
       <c r="L398" s="4"/>
       <c r="M398" s="4"/>
     </row>
-    <row r="399" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="4"/>
       <c r="B399" s="4"/>
       <c r="C399" s="4"/>
@@ -6883,7 +6848,7 @@
       <c r="L399" s="4"/>
       <c r="M399" s="4"/>
     </row>
-    <row r="400" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="4"/>
       <c r="B400" s="4"/>
       <c r="C400" s="4"/>
@@ -6898,7 +6863,7 @@
       <c r="L400" s="4"/>
       <c r="M400" s="4"/>
     </row>
-    <row r="401" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="4"/>
       <c r="B401" s="4"/>
       <c r="C401" s="4"/>
@@ -6913,7 +6878,7 @@
       <c r="L401" s="4"/>
       <c r="M401" s="4"/>
     </row>
-    <row r="402" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="4"/>
       <c r="B402" s="4"/>
       <c r="C402" s="4"/>
@@ -6928,7 +6893,7 @@
       <c r="L402" s="4"/>
       <c r="M402" s="4"/>
     </row>
-    <row r="403" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="4"/>
       <c r="B403" s="4"/>
       <c r="C403" s="4"/>
@@ -6943,7 +6908,7 @@
       <c r="L403" s="4"/>
       <c r="M403" s="4"/>
     </row>
-    <row r="404" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="4"/>
       <c r="B404" s="4"/>
       <c r="C404" s="4"/>
@@ -6958,7 +6923,7 @@
       <c r="L404" s="4"/>
       <c r="M404" s="4"/>
     </row>
-    <row r="405" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="4"/>
       <c r="B405" s="4"/>
       <c r="C405" s="4"/>
@@ -6973,7 +6938,7 @@
       <c r="L405" s="4"/>
       <c r="M405" s="4"/>
     </row>
-    <row r="406" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="4"/>
       <c r="B406" s="4"/>
       <c r="C406" s="4"/>
@@ -6988,7 +6953,7 @@
       <c r="L406" s="4"/>
       <c r="M406" s="4"/>
     </row>
-    <row r="407" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="4"/>
       <c r="B407" s="4"/>
       <c r="C407" s="4"/>
@@ -7003,7 +6968,7 @@
       <c r="L407" s="4"/>
       <c r="M407" s="4"/>
     </row>
-    <row r="408" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="4"/>
       <c r="B408" s="4"/>
       <c r="C408" s="4"/>
@@ -7018,7 +6983,7 @@
       <c r="L408" s="4"/>
       <c r="M408" s="4"/>
     </row>
-    <row r="409" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="4"/>
       <c r="B409" s="4"/>
       <c r="C409" s="4"/>
@@ -7033,7 +6998,7 @@
       <c r="L409" s="4"/>
       <c r="M409" s="4"/>
     </row>
-    <row r="410" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="4"/>
       <c r="B410" s="4"/>
       <c r="C410" s="4"/>
@@ -7048,7 +7013,7 @@
       <c r="L410" s="4"/>
       <c r="M410" s="4"/>
     </row>
-    <row r="411" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="4"/>
       <c r="B411" s="4"/>
       <c r="C411" s="4"/>
@@ -7063,7 +7028,7 @@
       <c r="L411" s="4"/>
       <c r="M411" s="4"/>
     </row>
-    <row r="412" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="4"/>
       <c r="B412" s="4"/>
       <c r="C412" s="4"/>
@@ -7078,7 +7043,7 @@
       <c r="L412" s="4"/>
       <c r="M412" s="4"/>
     </row>
-    <row r="413" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="4"/>
       <c r="B413" s="4"/>
       <c r="C413" s="4"/>
@@ -7093,7 +7058,7 @@
       <c r="L413" s="4"/>
       <c r="M413" s="4"/>
     </row>
-    <row r="414" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="4"/>
       <c r="B414" s="4"/>
       <c r="C414" s="4"/>
@@ -7108,7 +7073,7 @@
       <c r="L414" s="4"/>
       <c r="M414" s="4"/>
     </row>
-    <row r="415" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="4"/>
       <c r="B415" s="4"/>
       <c r="C415" s="4"/>
@@ -7123,7 +7088,7 @@
       <c r="L415" s="4"/>
       <c r="M415" s="4"/>
     </row>
-    <row r="416" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="4"/>
       <c r="B416" s="4"/>
       <c r="C416" s="4"/>
@@ -7138,7 +7103,7 @@
       <c r="L416" s="4"/>
       <c r="M416" s="4"/>
     </row>
-    <row r="417" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="4"/>
       <c r="B417" s="4"/>
       <c r="C417" s="4"/>
@@ -7153,7 +7118,7 @@
       <c r="L417" s="4"/>
       <c r="M417" s="4"/>
     </row>
-    <row r="418" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="4"/>
       <c r="B418" s="4"/>
       <c r="C418" s="4"/>
@@ -7168,7 +7133,7 @@
       <c r="L418" s="4"/>
       <c r="M418" s="4"/>
     </row>
-    <row r="419" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="4"/>
       <c r="B419" s="4"/>
       <c r="C419" s="4"/>
@@ -7183,7 +7148,7 @@
       <c r="L419" s="4"/>
       <c r="M419" s="4"/>
     </row>
-    <row r="420" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="4"/>
       <c r="B420" s="4"/>
       <c r="C420" s="4"/>
@@ -7198,7 +7163,7 @@
       <c r="L420" s="4"/>
       <c r="M420" s="4"/>
     </row>
-    <row r="421" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="4"/>
       <c r="B421" s="4"/>
       <c r="C421" s="4"/>
@@ -7213,7 +7178,7 @@
       <c r="L421" s="4"/>
       <c r="M421" s="4"/>
     </row>
-    <row r="422" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="4"/>
       <c r="B422" s="4"/>
       <c r="C422" s="4"/>
@@ -7228,7 +7193,7 @@
       <c r="L422" s="4"/>
       <c r="M422" s="4"/>
     </row>
-    <row r="423" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="4"/>
       <c r="B423" s="4"/>
       <c r="C423" s="4"/>
@@ -7243,7 +7208,7 @@
       <c r="L423" s="4"/>
       <c r="M423" s="4"/>
     </row>
-    <row r="424" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="4"/>
       <c r="B424" s="4"/>
       <c r="C424" s="4"/>
@@ -7258,7 +7223,7 @@
       <c r="L424" s="4"/>
       <c r="M424" s="4"/>
     </row>
-    <row r="425" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="4"/>
       <c r="B425" s="4"/>
       <c r="C425" s="4"/>
@@ -7273,7 +7238,7 @@
       <c r="L425" s="4"/>
       <c r="M425" s="4"/>
     </row>
-    <row r="426" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="4"/>
       <c r="B426" s="4"/>
       <c r="C426" s="4"/>
@@ -7288,7 +7253,7 @@
       <c r="L426" s="4"/>
       <c r="M426" s="4"/>
     </row>
-    <row r="427" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="4"/>
       <c r="B427" s="4"/>
       <c r="C427" s="4"/>
@@ -7303,7 +7268,7 @@
       <c r="L427" s="4"/>
       <c r="M427" s="4"/>
     </row>
-    <row r="428" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="4"/>
       <c r="B428" s="4"/>
       <c r="C428" s="4"/>
@@ -7318,7 +7283,7 @@
       <c r="L428" s="4"/>
       <c r="M428" s="4"/>
     </row>
-    <row r="429" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="4"/>
       <c r="B429" s="4"/>
       <c r="C429" s="4"/>
@@ -7333,7 +7298,7 @@
       <c r="L429" s="4"/>
       <c r="M429" s="4"/>
     </row>
-    <row r="430" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="4"/>
       <c r="B430" s="4"/>
       <c r="C430" s="4"/>
@@ -7348,7 +7313,7 @@
       <c r="L430" s="4"/>
       <c r="M430" s="4"/>
     </row>
-    <row r="431" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="4"/>
       <c r="B431" s="4"/>
       <c r="C431" s="4"/>
@@ -7363,7 +7328,7 @@
       <c r="L431" s="4"/>
       <c r="M431" s="4"/>
     </row>
-    <row r="432" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="4"/>
       <c r="B432" s="4"/>
       <c r="C432" s="4"/>
@@ -7378,7 +7343,7 @@
       <c r="L432" s="4"/>
       <c r="M432" s="4"/>
     </row>
-    <row r="433" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="4"/>
       <c r="B433" s="4"/>
       <c r="C433" s="4"/>
@@ -7393,7 +7358,7 @@
       <c r="L433" s="4"/>
       <c r="M433" s="4"/>
     </row>
-    <row r="434" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="4"/>
       <c r="B434" s="4"/>
       <c r="C434" s="4"/>
@@ -7408,7 +7373,7 @@
       <c r="L434" s="4"/>
       <c r="M434" s="4"/>
     </row>
-    <row r="435" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="4"/>
       <c r="B435" s="4"/>
       <c r="C435" s="4"/>
@@ -7423,7 +7388,7 @@
       <c r="L435" s="4"/>
       <c r="M435" s="4"/>
     </row>
-    <row r="436" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="4"/>
       <c r="B436" s="4"/>
       <c r="C436" s="4"/>
@@ -7438,7 +7403,7 @@
       <c r="L436" s="4"/>
       <c r="M436" s="4"/>
     </row>
-    <row r="437" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="4"/>
       <c r="B437" s="4"/>
       <c r="C437" s="4"/>
@@ -7453,7 +7418,7 @@
       <c r="L437" s="4"/>
       <c r="M437" s="4"/>
     </row>
-    <row r="438" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="4"/>
       <c r="B438" s="4"/>
       <c r="C438" s="4"/>
@@ -7468,7 +7433,7 @@
       <c r="L438" s="4"/>
       <c r="M438" s="4"/>
     </row>
-    <row r="439" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="4"/>
       <c r="B439" s="4"/>
       <c r="C439" s="4"/>
@@ -7483,7 +7448,7 @@
       <c r="L439" s="4"/>
       <c r="M439" s="4"/>
     </row>
-    <row r="440" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="4"/>
       <c r="B440" s="4"/>
       <c r="C440" s="4"/>
@@ -7498,7 +7463,7 @@
       <c r="L440" s="4"/>
       <c r="M440" s="4"/>
     </row>
-    <row r="441" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="4"/>
       <c r="B441" s="4"/>
       <c r="C441" s="4"/>
@@ -7513,7 +7478,7 @@
       <c r="L441" s="4"/>
       <c r="M441" s="4"/>
     </row>
-    <row r="442" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="4"/>
       <c r="B442" s="4"/>
       <c r="C442" s="4"/>
@@ -7528,7 +7493,7 @@
       <c r="L442" s="4"/>
       <c r="M442" s="4"/>
     </row>
-    <row r="443" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="4"/>
       <c r="B443" s="4"/>
       <c r="C443" s="4"/>
@@ -7543,7 +7508,7 @@
       <c r="L443" s="4"/>
       <c r="M443" s="4"/>
     </row>
-    <row r="444" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="4"/>
       <c r="B444" s="4"/>
       <c r="C444" s="4"/>
@@ -7558,7 +7523,7 @@
       <c r="L444" s="4"/>
       <c r="M444" s="4"/>
     </row>
-    <row r="445" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="4"/>
       <c r="B445" s="4"/>
       <c r="C445" s="4"/>
@@ -7573,7 +7538,7 @@
       <c r="L445" s="4"/>
       <c r="M445" s="4"/>
     </row>
-    <row r="446" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="4"/>
       <c r="B446" s="4"/>
       <c r="C446" s="4"/>
@@ -7588,7 +7553,7 @@
       <c r="L446" s="4"/>
       <c r="M446" s="4"/>
     </row>
-    <row r="447" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="4"/>
       <c r="B447" s="4"/>
       <c r="C447" s="4"/>
@@ -7603,7 +7568,7 @@
       <c r="L447" s="4"/>
       <c r="M447" s="4"/>
     </row>
-    <row r="448" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="4"/>
       <c r="B448" s="4"/>
       <c r="C448" s="4"/>
@@ -7618,7 +7583,7 @@
       <c r="L448" s="4"/>
       <c r="M448" s="4"/>
     </row>
-    <row r="449" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="4"/>
       <c r="B449" s="4"/>
       <c r="C449" s="4"/>
@@ -7633,7 +7598,7 @@
       <c r="L449" s="4"/>
       <c r="M449" s="4"/>
     </row>
-    <row r="450" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="4"/>
       <c r="B450" s="4"/>
       <c r="C450" s="4"/>
@@ -7648,7 +7613,7 @@
       <c r="L450" s="4"/>
       <c r="M450" s="4"/>
     </row>
-    <row r="451" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="4"/>
       <c r="B451" s="4"/>
       <c r="C451" s="4"/>
@@ -7663,7 +7628,7 @@
       <c r="L451" s="4"/>
       <c r="M451" s="4"/>
     </row>
-    <row r="452" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="4"/>
       <c r="B452" s="4"/>
       <c r="C452" s="4"/>
@@ -7678,7 +7643,7 @@
       <c r="L452" s="4"/>
       <c r="M452" s="4"/>
     </row>
-    <row r="453" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="4"/>
       <c r="B453" s="4"/>
       <c r="C453" s="4"/>
@@ -7693,7 +7658,7 @@
       <c r="L453" s="4"/>
       <c r="M453" s="4"/>
     </row>
-    <row r="454" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="4"/>
       <c r="B454" s="4"/>
       <c r="C454" s="4"/>
@@ -7708,7 +7673,7 @@
       <c r="L454" s="4"/>
       <c r="M454" s="4"/>
     </row>
-    <row r="455" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="4"/>
       <c r="B455" s="4"/>
       <c r="C455" s="4"/>
@@ -7723,7 +7688,7 @@
       <c r="L455" s="4"/>
       <c r="M455" s="4"/>
     </row>
-    <row r="456" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="4"/>
       <c r="B456" s="4"/>
       <c r="C456" s="4"/>
@@ -7738,7 +7703,7 @@
       <c r="L456" s="4"/>
       <c r="M456" s="4"/>
     </row>
-    <row r="457" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="4"/>
       <c r="B457" s="4"/>
       <c r="C457" s="4"/>
@@ -7753,7 +7718,7 @@
       <c r="L457" s="4"/>
       <c r="M457" s="4"/>
     </row>
-    <row r="458" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="4"/>
       <c r="B458" s="4"/>
       <c r="C458" s="4"/>
@@ -7768,7 +7733,7 @@
       <c r="L458" s="4"/>
       <c r="M458" s="4"/>
     </row>
-    <row r="459" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="4"/>
       <c r="B459" s="4"/>
       <c r="C459" s="4"/>
@@ -7783,7 +7748,7 @@
       <c r="L459" s="4"/>
       <c r="M459" s="4"/>
     </row>
-    <row r="460" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="4"/>
       <c r="B460" s="4"/>
       <c r="C460" s="4"/>
@@ -7798,7 +7763,7 @@
       <c r="L460" s="4"/>
       <c r="M460" s="4"/>
     </row>
-    <row r="461" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="4"/>
       <c r="B461" s="4"/>
       <c r="C461" s="4"/>
@@ -7813,7 +7778,7 @@
       <c r="L461" s="4"/>
       <c r="M461" s="4"/>
     </row>
-    <row r="462" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="4"/>
       <c r="B462" s="4"/>
       <c r="C462" s="4"/>
@@ -7828,7 +7793,7 @@
       <c r="L462" s="4"/>
       <c r="M462" s="4"/>
     </row>
-    <row r="463" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="4"/>
       <c r="B463" s="4"/>
       <c r="C463" s="4"/>
@@ -7843,7 +7808,7 @@
       <c r="L463" s="4"/>
       <c r="M463" s="4"/>
     </row>
-    <row r="464" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="4"/>
       <c r="B464" s="4"/>
       <c r="C464" s="4"/>
@@ -7858,7 +7823,7 @@
       <c r="L464" s="4"/>
       <c r="M464" s="4"/>
     </row>
-    <row r="465" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="4"/>
       <c r="B465" s="4"/>
       <c r="C465" s="4"/>
@@ -7873,7 +7838,7 @@
       <c r="L465" s="4"/>
       <c r="M465" s="4"/>
     </row>
-    <row r="466" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="4"/>
       <c r="B466" s="4"/>
       <c r="C466" s="4"/>
@@ -7888,7 +7853,7 @@
       <c r="L466" s="4"/>
       <c r="M466" s="4"/>
     </row>
-    <row r="467" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="4"/>
       <c r="B467" s="4"/>
       <c r="C467" s="4"/>
@@ -7903,7 +7868,7 @@
       <c r="L467" s="4"/>
       <c r="M467" s="4"/>
     </row>
-    <row r="468" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="4"/>
       <c r="B468" s="4"/>
       <c r="C468" s="4"/>
@@ -7918,7 +7883,7 @@
       <c r="L468" s="4"/>
       <c r="M468" s="4"/>
     </row>
-    <row r="469" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="4"/>
       <c r="B469" s="4"/>
       <c r="C469" s="4"/>
@@ -7933,7 +7898,7 @@
       <c r="L469" s="4"/>
       <c r="M469" s="4"/>
     </row>
-    <row r="470" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="4"/>
       <c r="B470" s="4"/>
       <c r="C470" s="4"/>
@@ -7948,7 +7913,7 @@
       <c r="L470" s="4"/>
       <c r="M470" s="4"/>
     </row>
-    <row r="471" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="4"/>
       <c r="B471" s="4"/>
       <c r="C471" s="4"/>
@@ -7963,7 +7928,7 @@
       <c r="L471" s="4"/>
       <c r="M471" s="4"/>
     </row>
-    <row r="472" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="4"/>
       <c r="B472" s="4"/>
       <c r="C472" s="4"/>
@@ -7978,7 +7943,7 @@
       <c r="L472" s="4"/>
       <c r="M472" s="4"/>
     </row>
-    <row r="473" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="4"/>
       <c r="B473" s="4"/>
       <c r="C473" s="4"/>
@@ -7993,7 +7958,7 @@
       <c r="L473" s="4"/>
       <c r="M473" s="4"/>
     </row>
-    <row r="474" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="4"/>
       <c r="B474" s="4"/>
       <c r="C474" s="4"/>
@@ -8008,7 +7973,7 @@
       <c r="L474" s="4"/>
       <c r="M474" s="4"/>
     </row>
-    <row r="475" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="4"/>
       <c r="B475" s="4"/>
       <c r="C475" s="4"/>
@@ -8023,7 +7988,7 @@
       <c r="L475" s="4"/>
       <c r="M475" s="4"/>
     </row>
-    <row r="476" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="4"/>
       <c r="B476" s="4"/>
       <c r="C476" s="4"/>
@@ -8038,7 +8003,7 @@
       <c r="L476" s="4"/>
       <c r="M476" s="4"/>
     </row>
-    <row r="477" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="4"/>
       <c r="B477" s="4"/>
       <c r="C477" s="4"/>
@@ -8053,7 +8018,7 @@
       <c r="L477" s="4"/>
       <c r="M477" s="4"/>
     </row>
-    <row r="478" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="4"/>
       <c r="B478" s="4"/>
       <c r="C478" s="4"/>
@@ -8068,7 +8033,7 @@
       <c r="L478" s="4"/>
       <c r="M478" s="4"/>
     </row>
-    <row r="479" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="4"/>
       <c r="B479" s="4"/>
       <c r="C479" s="4"/>
@@ -8083,7 +8048,7 @@
       <c r="L479" s="4"/>
       <c r="M479" s="4"/>
     </row>
-    <row r="480" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="4"/>
       <c r="B480" s="4"/>
       <c r="C480" s="4"/>
@@ -8098,7 +8063,7 @@
       <c r="L480" s="4"/>
       <c r="M480" s="4"/>
     </row>
-    <row r="481" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A481" s="4"/>
       <c r="B481" s="4"/>
       <c r="C481" s="4"/>
@@ -8113,7 +8078,7 @@
       <c r="L481" s="4"/>
       <c r="M481" s="4"/>
     </row>
-    <row r="482" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A482" s="4"/>
       <c r="B482" s="4"/>
       <c r="C482" s="4"/>
@@ -8128,7 +8093,7 @@
       <c r="L482" s="4"/>
       <c r="M482" s="4"/>
     </row>
-    <row r="483" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A483" s="4"/>
       <c r="B483" s="4"/>
       <c r="C483" s="4"/>
@@ -8143,7 +8108,7 @@
       <c r="L483" s="4"/>
       <c r="M483" s="4"/>
     </row>
-    <row r="484" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A484" s="4"/>
       <c r="B484" s="4"/>
       <c r="C484" s="4"/>
@@ -8158,7 +8123,7 @@
       <c r="L484" s="4"/>
       <c r="M484" s="4"/>
     </row>
-    <row r="485" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="4"/>
       <c r="B485" s="4"/>
       <c r="C485" s="4"/>
@@ -8173,7 +8138,7 @@
       <c r="L485" s="4"/>
       <c r="M485" s="4"/>
     </row>
-    <row r="486" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A486" s="4"/>
       <c r="B486" s="4"/>
       <c r="C486" s="4"/>
@@ -8188,7 +8153,7 @@
       <c r="L486" s="4"/>
       <c r="M486" s="4"/>
     </row>
-    <row r="487" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="4"/>
       <c r="B487" s="4"/>
       <c r="C487" s="4"/>
@@ -8203,7 +8168,7 @@
       <c r="L487" s="4"/>
       <c r="M487" s="4"/>
     </row>
-    <row r="488" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A488" s="4"/>
       <c r="B488" s="4"/>
       <c r="C488" s="4"/>
@@ -8218,7 +8183,7 @@
       <c r="L488" s="4"/>
       <c r="M488" s="4"/>
     </row>
-    <row r="489" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A489" s="4"/>
       <c r="B489" s="4"/>
       <c r="C489" s="4"/>
@@ -8233,7 +8198,7 @@
       <c r="L489" s="4"/>
       <c r="M489" s="4"/>
     </row>
-    <row r="490" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A490" s="4"/>
       <c r="B490" s="4"/>
       <c r="C490" s="4"/>
@@ -8248,7 +8213,7 @@
       <c r="L490" s="4"/>
       <c r="M490" s="4"/>
     </row>
-    <row r="491" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A491" s="4"/>
       <c r="B491" s="4"/>
       <c r="C491" s="4"/>
@@ -8263,7 +8228,7 @@
       <c r="L491" s="4"/>
       <c r="M491" s="4"/>
     </row>
-    <row r="492" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A492" s="4"/>
       <c r="B492" s="4"/>
       <c r="C492" s="4"/>
@@ -8278,7 +8243,7 @@
       <c r="L492" s="4"/>
       <c r="M492" s="4"/>
     </row>
-    <row r="493" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A493" s="4"/>
       <c r="B493" s="4"/>
       <c r="C493" s="4"/>
@@ -8293,7 +8258,7 @@
       <c r="L493" s="4"/>
       <c r="M493" s="4"/>
     </row>
-    <row r="494" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A494" s="4"/>
       <c r="B494" s="4"/>
       <c r="C494" s="4"/>
@@ -8308,7 +8273,7 @@
       <c r="L494" s="4"/>
       <c r="M494" s="4"/>
     </row>
-    <row r="495" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A495" s="4"/>
       <c r="B495" s="4"/>
       <c r="C495" s="4"/>
@@ -8323,7 +8288,7 @@
       <c r="L495" s="4"/>
       <c r="M495" s="4"/>
     </row>
-    <row r="496" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A496" s="4"/>
       <c r="B496" s="4"/>
       <c r="C496" s="4"/>
@@ -8338,7 +8303,7 @@
       <c r="L496" s="4"/>
       <c r="M496" s="4"/>
     </row>
-    <row r="497" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="4"/>
       <c r="B497" s="4"/>
       <c r="C497" s="4"/>
@@ -8353,7 +8318,7 @@
       <c r="L497" s="4"/>
       <c r="M497" s="4"/>
     </row>
-    <row r="498" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="4"/>
       <c r="B498" s="4"/>
       <c r="C498" s="4"/>
@@ -8368,7 +8333,7 @@
       <c r="L498" s="4"/>
       <c r="M498" s="4"/>
     </row>
-    <row r="499" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A499" s="4"/>
       <c r="B499" s="4"/>
       <c r="C499" s="4"/>
@@ -8383,7 +8348,7 @@
       <c r="L499" s="4"/>
       <c r="M499" s="4"/>
     </row>
-    <row r="500" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A500" s="4"/>
       <c r="B500" s="4"/>
       <c r="C500" s="4"/>
@@ -8399,9 +8364,10 @@
       <c r="M500" s="4"/>
     </row>
   </sheetData>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
@@ -8409,175 +8375,201 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="8"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="9" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>29</v>
+    <row r="1" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="8"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="9" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>51</v>
+    <row r="1" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:Q1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="8"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="9" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>65</v>
+    <row r="1" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:D50"/>
-  <sheetFormatPr defaultColWidth="13.28515625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.2890625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="45.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="26.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="13.28515625" style="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="14.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="45.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="18.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="26.42"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="1" width="13.29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
         <v>7</v>
       </c>
@@ -8585,310 +8577,311 @@
         <v>8</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
     </row>
-    <row r="3" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
     </row>
-    <row r="4" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
     </row>
-    <row r="5" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
     </row>
-    <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
     </row>
-    <row r="8" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
     </row>
-    <row r="9" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
     </row>
-    <row r="10" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
     </row>
-    <row r="11" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
     </row>
-    <row r="12" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
     </row>
-    <row r="13" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
     </row>
-    <row r="15" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
     </row>
-    <row r="17" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
     </row>
-    <row r="18" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
     </row>
-    <row r="19" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
     </row>
-    <row r="20" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
     </row>
-    <row r="22" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
     </row>
-    <row r="23" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
     </row>
-    <row r="24" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
     </row>
-    <row r="25" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
     </row>
-    <row r="26" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
     </row>
-    <row r="27" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
     </row>
-    <row r="28" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
     </row>
-    <row r="29" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
     </row>
-    <row r="30" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
     </row>
-    <row r="31" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
     </row>
-    <row r="32" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
     </row>
-    <row r="33" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
     </row>
-    <row r="34" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
     </row>
-    <row r="35" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
     </row>
-    <row r="36" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
     </row>
-    <row r="37" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
     </row>
-    <row r="38" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
     </row>
-    <row r="39" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
     </row>
-    <row r="40" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
     </row>
-    <row r="42" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
     </row>
-    <row r="44" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
     </row>
-    <row r="46" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
     </row>
-    <row r="47" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
     </row>
-    <row r="48" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
     </row>
-    <row r="49" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
     </row>
-    <row r="50" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
     </row>
   </sheetData>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
@@ -8896,1287 +8889,1434 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F100"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="37.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.42"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="1" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+    <row r="1" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="C3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="F3" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="B4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="C4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="E4" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="11" t="s">
+      <c r="F4" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B23" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="11" t="s">
+      <c r="C23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="11" t="b">
+      <c r="B24" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="8" t="b">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B25" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="11" t="s">
+      <c r="C25" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="B26" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F4" s="11"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
+      <c r="C26" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B27" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B6" s="11" t="s">
+      <c r="B28" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
+      <c r="C28" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B29" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+      <c r="C29" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B30" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
+      <c r="B31" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="C31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
+      <c r="B32" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="11"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="11"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="11"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="11"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="11"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="11"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="11"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="11"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="11"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="11"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="11"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="11"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" s="11"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" s="11"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" s="11"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="11"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" s="11"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="11"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" s="11"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" s="11"/>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" s="11"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="11"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" s="11"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="11"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" s="11"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="11"/>
-      <c r="B58" s="11"/>
-      <c r="C58" s="11"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" s="11"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" s="11"/>
-      <c r="B60" s="11"/>
-      <c r="C60" s="11"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" s="11"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="11"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" s="11"/>
-      <c r="B62" s="11"/>
-      <c r="C62" s="11"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" s="11"/>
-      <c r="B63" s="11"/>
-      <c r="C63" s="11"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="11"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" s="11"/>
-      <c r="B64" s="11"/>
-      <c r="C64" s="11"/>
-      <c r="D64" s="11"/>
-      <c r="E64" s="11"/>
-      <c r="F64" s="11"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" s="11"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="11"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="11"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="11"/>
-      <c r="B66" s="11"/>
-      <c r="C66" s="11"/>
-      <c r="D66" s="11"/>
-      <c r="E66" s="11"/>
-      <c r="F66" s="11"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A67" s="11"/>
-      <c r="B67" s="11"/>
-      <c r="C67" s="11"/>
-      <c r="D67" s="11"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="11"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A68" s="11"/>
-      <c r="B68" s="11"/>
-      <c r="C68" s="11"/>
-      <c r="D68" s="11"/>
-      <c r="E68" s="11"/>
-      <c r="F68" s="11"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A69" s="11"/>
-      <c r="B69" s="11"/>
-      <c r="C69" s="11"/>
-      <c r="D69" s="11"/>
-      <c r="E69" s="11"/>
-      <c r="F69" s="11"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A70" s="11"/>
-      <c r="B70" s="11"/>
-      <c r="C70" s="11"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="11"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A71" s="11"/>
-      <c r="B71" s="11"/>
-      <c r="C71" s="11"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="11"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A72" s="11"/>
-      <c r="B72" s="11"/>
-      <c r="C72" s="11"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="11"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A73" s="11"/>
-      <c r="B73" s="11"/>
-      <c r="C73" s="11"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="11"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A74" s="11"/>
-      <c r="B74" s="11"/>
-      <c r="C74" s="11"/>
-      <c r="D74" s="11"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="11"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A75" s="11"/>
-      <c r="B75" s="11"/>
-      <c r="C75" s="11"/>
-      <c r="D75" s="11"/>
-      <c r="E75" s="11"/>
-      <c r="F75" s="11"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A76" s="11"/>
-      <c r="B76" s="11"/>
-      <c r="C76" s="11"/>
-      <c r="D76" s="11"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="11"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A77" s="11"/>
-      <c r="B77" s="11"/>
-      <c r="C77" s="11"/>
-      <c r="D77" s="11"/>
-      <c r="E77" s="11"/>
-      <c r="F77" s="11"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A78" s="11"/>
-      <c r="B78" s="11"/>
-      <c r="C78" s="11"/>
-      <c r="D78" s="11"/>
-      <c r="E78" s="11"/>
-      <c r="F78" s="11"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A79" s="11"/>
-      <c r="B79" s="11"/>
-      <c r="C79" s="11"/>
-      <c r="D79" s="11"/>
-      <c r="E79" s="11"/>
-      <c r="F79" s="11"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" s="11"/>
-      <c r="B80" s="11"/>
-      <c r="C80" s="11"/>
-      <c r="D80" s="11"/>
-      <c r="E80" s="11"/>
-      <c r="F80" s="11"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A81" s="11"/>
-      <c r="B81" s="11"/>
-      <c r="C81" s="11"/>
-      <c r="D81" s="11"/>
-      <c r="E81" s="11"/>
-      <c r="F81" s="11"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A82" s="11"/>
-      <c r="B82" s="11"/>
-      <c r="C82" s="11"/>
-      <c r="D82" s="11"/>
-      <c r="E82" s="11"/>
-      <c r="F82" s="11"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A83" s="11"/>
-      <c r="B83" s="11"/>
-      <c r="C83" s="11"/>
-      <c r="D83" s="11"/>
-      <c r="E83" s="11"/>
-      <c r="F83" s="11"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A84" s="11"/>
-      <c r="B84" s="11"/>
-      <c r="C84" s="11"/>
-      <c r="D84" s="11"/>
-      <c r="E84" s="11"/>
-      <c r="F84" s="11"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A85" s="11"/>
-      <c r="B85" s="11"/>
-      <c r="C85" s="11"/>
-      <c r="D85" s="11"/>
-      <c r="E85" s="11"/>
-      <c r="F85" s="11"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A86" s="11"/>
-      <c r="B86" s="11"/>
-      <c r="C86" s="11"/>
-      <c r="D86" s="11"/>
-      <c r="E86" s="11"/>
-      <c r="F86" s="11"/>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A87" s="11"/>
-      <c r="B87" s="11"/>
-      <c r="C87" s="11"/>
-      <c r="D87" s="11"/>
-      <c r="E87" s="11"/>
-      <c r="F87" s="11"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A88" s="11"/>
-      <c r="B88" s="11"/>
-      <c r="C88" s="11"/>
-      <c r="D88" s="11"/>
-      <c r="E88" s="11"/>
-      <c r="F88" s="11"/>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A89" s="11"/>
-      <c r="B89" s="11"/>
-      <c r="C89" s="11"/>
-      <c r="D89" s="11"/>
-      <c r="E89" s="11"/>
-      <c r="F89" s="11"/>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A90" s="11"/>
-      <c r="B90" s="11"/>
-      <c r="C90" s="11"/>
-      <c r="D90" s="11"/>
-      <c r="E90" s="11"/>
-      <c r="F90" s="11"/>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A91" s="11"/>
-      <c r="B91" s="11"/>
-      <c r="C91" s="11"/>
-      <c r="D91" s="11"/>
-      <c r="E91" s="11"/>
-      <c r="F91" s="11"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A92" s="11"/>
-      <c r="B92" s="11"/>
-      <c r="C92" s="11"/>
-      <c r="D92" s="11"/>
-      <c r="E92" s="11"/>
-      <c r="F92" s="11"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A93" s="11"/>
-      <c r="B93" s="11"/>
-      <c r="C93" s="11"/>
-      <c r="D93" s="11"/>
-      <c r="E93" s="11"/>
-      <c r="F93" s="11"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A94" s="11"/>
-      <c r="B94" s="11"/>
-      <c r="C94" s="11"/>
-      <c r="D94" s="11"/>
-      <c r="E94" s="11"/>
-      <c r="F94" s="11"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A95" s="11"/>
-      <c r="B95" s="11"/>
-      <c r="C95" s="11"/>
-      <c r="D95" s="11"/>
-      <c r="E95" s="11"/>
-      <c r="F95" s="11"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A96" s="11"/>
-      <c r="B96" s="11"/>
-      <c r="C96" s="11"/>
-      <c r="D96" s="11"/>
-      <c r="E96" s="11"/>
-      <c r="F96" s="11"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A97" s="11"/>
-      <c r="B97" s="11"/>
-      <c r="C97" s="11"/>
-      <c r="D97" s="11"/>
-      <c r="E97" s="11"/>
-      <c r="F97" s="11"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A98" s="11"/>
-      <c r="B98" s="11"/>
-      <c r="C98" s="11"/>
-      <c r="D98" s="11"/>
-      <c r="E98" s="11"/>
-      <c r="F98" s="11"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A99" s="11"/>
-      <c r="B99" s="11"/>
-      <c r="C99" s="11"/>
-      <c r="D99" s="11"/>
-      <c r="E99" s="11"/>
-      <c r="F99" s="11"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A100" s="11"/>
-      <c r="B100" s="11"/>
-      <c r="C100" s="11"/>
-      <c r="D100" s="11"/>
-      <c r="E100" s="11"/>
-      <c r="F100" s="11"/>
+      <c r="C32" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="8" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="4"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+    </row>
+    <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+    </row>
+    <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="4"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+    </row>
+    <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="4"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="4"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+    </row>
+    <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="4"/>
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="4"/>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+    </row>
+    <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="4"/>
+      <c r="B87" s="4"/>
+      <c r="C87" s="4"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="4"/>
+      <c r="B88" s="4"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="4"/>
+      <c r="B89" s="4"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+    </row>
+    <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="4"/>
+      <c r="B90" s="4"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+    </row>
+    <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="4"/>
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="4"/>
+      <c r="B92" s="4"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+    </row>
+    <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="4"/>
+      <c r="B93" s="4"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+    </row>
+    <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="4"/>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+    </row>
+    <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="4"/>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="4"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="4"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+    </row>
+    <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="4"/>
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="4"/>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+    </row>
+    <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="4"/>
+      <c r="B98" s="4"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="4"/>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+    </row>
+    <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="4"/>
+      <c r="B99" s="4"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="4"/>
+      <c r="B100" s="4"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="8"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="9" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>29</v>
+    <row r="1" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="8"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="9" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>29</v>
+    <row r="1" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="8"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="9" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>51</v>
+    <row r="1" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:Q1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="8"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="9" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>65</v>
+    <row r="1" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="8"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="9" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>29</v>
+    <row r="1" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="8"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="9" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>29</v>
+    <row r="1" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>